--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.18717778795901</v>
+        <v>1.187179901244115</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178871650834505</v>
+        <v>1.178875001146447</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177378764334548</v>
+        <v>1.17738168306097</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172919796129255</v>
+        <v>1.172923909065515</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171691409947492</v>
+        <v>1.171695716968526</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169671682747763</v>
+        <v>1.169676130017628</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167203765528434</v>
+        <v>1.167208250695462</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165463007451099</v>
+        <v>1.16546746827294</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166474705329052</v>
+        <v>1.166477750834885</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161095791922017</v>
+        <v>1.161095350952699</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161576357357582</v>
+        <v>1.16157607886358</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.16092614479306</v>
+        <v>1.160925930244203</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162136183129206</v>
+        <v>1.162134568788128</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159749460499713</v>
+        <v>1.15974866931887</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541565953449</v>
+        <v>1.155415713094641</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148465310948314</v>
+        <v>1.148465819471171</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143141860710935</v>
+        <v>1.143141753137004</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137889053154339</v>
+        <v>1.137887774004294</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130166531102364</v>
+        <v>1.130163152351843</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125017639790652</v>
+        <v>1.12501338186297</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129869680591068</v>
+        <v>1.129860334018903</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136945155829395</v>
+        <v>1.136931883825395</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14294583626381</v>
+        <v>1.142923720331176</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146301848180843</v>
+        <v>1.146276031840622</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146185616218527</v>
+        <v>1.146154721333774</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140440933191652</v>
+        <v>1.14040861566425</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138855997884184</v>
+        <v>1.138822038665889</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138732265866479</v>
+        <v>1.13869636651595</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150309743008843</v>
+        <v>1.150286153713077</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165789351313944</v>
+        <v>1.165773605929549</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166239754045718</v>
+        <v>1.16622501591107</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180611715935355</v>
+        <v>1.180609291074701</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.19149549579248</v>
+        <v>1.191507450658487</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199694273900093</v>
+        <v>1.199708704396029</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.21140403631844</v>
+        <v>1.211425186844688</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205661622031162</v>
+        <v>1.205668802758685</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206437282648754</v>
+        <v>1.206449215781906</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210051383855798</v>
+        <v>1.210077675495994</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215734252026183</v>
+        <v>1.21577244714263</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221893892942855</v>
+        <v>1.221937942478145</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220601535461156</v>
+        <v>1.22063557891956</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208155800371506</v>
+        <v>1.208186347224084</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199870215574894</v>
+        <v>1.199899054872078</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189274353381796</v>
+        <v>1.189296097054716</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180946320934833</v>
+        <v>1.180964595320479</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175747465243053</v>
+        <v>1.175761177538913</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172296128889161</v>
+        <v>1.17230533463757</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173555374557277</v>
+        <v>1.173570874134764</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169627506612142</v>
+        <v>1.169637448698839</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168393303408847</v>
+        <v>1.168404915253014</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168435489448388</v>
+        <v>1.168454096496299</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166336727502901</v>
+        <v>1.166352782558921</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158123890665471</v>
+        <v>1.158136159820367</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151689881736541</v>
+        <v>1.151707220506723</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146128461346466</v>
+        <v>1.146145825182833</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143768291535095</v>
+        <v>1.143777721325824</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144590429626793</v>
+        <v>1.144586685313685</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146924691695088</v>
+        <v>1.146909375841503</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149902968519102</v>
+        <v>1.149871812990489</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151452590074888</v>
+        <v>1.151410457957668</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150924735187069</v>
+        <v>1.151192914303151</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.148506522348387</v>
+        <v>1.148816366340652</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.146560353521602</v>
+        <v>1.146949156446336</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.145647187601594</v>
+        <v>1.146110380212155</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.14529471257939</v>
+        <v>1.145846299843704</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.145077065701828</v>
+        <v>1.145737611323796</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.146295804364907</v>
+        <v>1.147004078852127</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.151038675977144</v>
+        <v>1.1517487056833</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.154355013740909</v>
+        <v>1.155151215129471</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.158316903846789</v>
+        <v>1.159326228655052</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.164651446126515</v>
+        <v>1.165821717423208</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.175266202159758</v>
+        <v>1.176382061886346</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.171814559613975</v>
+        <v>1.173897203654094</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.185414939501377</v>
+        <v>1.187180611507029</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187179901244115</v>
+        <v>1.187181970043989</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178875001146447</v>
+        <v>1.178878281123758</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17738168306097</v>
+        <v>1.177384541010027</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172923909065515</v>
+        <v>1.172927936128662</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171695716968526</v>
+        <v>1.171699934008554</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169676130017628</v>
+        <v>1.169680484324947</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167208250695462</v>
+        <v>1.167212642082881</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.16546746827294</v>
+        <v>1.165471835821793</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166477750834885</v>
+        <v>1.166480733765293</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161095350952699</v>
+        <v>1.161094919596168</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.16157607886358</v>
+        <v>1.161575806546584</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160925930244203</v>
+        <v>1.160925720518107</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162134568788128</v>
+        <v>1.162132989027633</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15974866931887</v>
+        <v>1.15974789501525</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415713094641</v>
+        <v>1.155415765987292</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148465819471171</v>
+        <v>1.148466319112513</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143141753137004</v>
+        <v>1.143141650865603</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137887774004294</v>
+        <v>1.137886526372916</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130163152351843</v>
+        <v>1.130159848433796</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.12501338186297</v>
+        <v>1.125009216676208</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129860334018903</v>
+        <v>1.129851187759779</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136931883825395</v>
+        <v>1.136918894592068</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142923720331176</v>
+        <v>1.142902066667052</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146276031840622</v>
+        <v>1.146250753167858</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146154721333774</v>
+        <v>1.146124468196532</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.14040861566425</v>
+        <v>1.140376965113386</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138822038665889</v>
+        <v>1.13878877615123</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.13869636651595</v>
+        <v>1.138661198322834</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150286153713077</v>
+        <v>1.150263040713353</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165773605929549</v>
+        <v>1.165758179324644</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.16622501591107</v>
+        <v>1.166210573201054</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180609291074701</v>
+        <v>1.18060691238498</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191507450658487</v>
+        <v>1.191519164827279</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199708704396029</v>
+        <v>1.199722843090615</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211425186844688</v>
+        <v>1.211445900883562</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205668802758685</v>
+        <v>1.205675815113205</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206449215781906</v>
+        <v>1.206460878346754</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210077675495994</v>
+        <v>1.21010340363613</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.21577244714263</v>
+        <v>1.215809843162684</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221937942478145</v>
+        <v>1.221981073391731</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.22063557891956</v>
+        <v>1.220668903441846</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208186347224084</v>
+        <v>1.20821625431845</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199899054872078</v>
+        <v>1.199927294209718</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189296097054716</v>
+        <v>1.189317396032939</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180964595320479</v>
+        <v>1.180982498143994</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175761177538913</v>
+        <v>1.175774612397896</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.17230533463757</v>
+        <v>1.172314353617138</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173570874134764</v>
+        <v>1.173586056652379</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169637448698839</v>
+        <v>1.169647181552147</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168404915253014</v>
+        <v>1.168416282280316</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168454096496299</v>
+        <v>1.168472318017013</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166352782558921</v>
+        <v>1.166368503372976</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158136159820367</v>
+        <v>1.15814816626876</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151707220506723</v>
+        <v>1.151724207480517</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146145825182833</v>
+        <v>1.146162849649893</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143777721325824</v>
+        <v>1.143786989519702</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144586685313685</v>
+        <v>1.144583060924491</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146909375841503</v>
+        <v>1.146894404270362</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149871812990489</v>
+        <v>1.149841311181897</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151410457957668</v>
+        <v>1.151369157565837</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.151192914303151</v>
+        <v>1.15114240785387</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.148816366340652</v>
+        <v>1.149132668417421</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.146949156446336</v>
+        <v>1.147349686989078</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.146110380212155</v>
+        <v>1.146510389227269</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.145846299843704</v>
+        <v>1.146228672599524</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.145737611323796</v>
+        <v>1.146074587701695</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.147004078852127</v>
+        <v>1.147265971250515</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.1517487056833</v>
+        <v>1.151874286677462</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.155151215129471</v>
+        <v>1.155207140750598</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.159326228655052</v>
+        <v>1.159298438555642</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.165821717423208</v>
+        <v>1.165578118736353</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.176382061886346</v>
+        <v>1.175613707871902</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.173897203654094</v>
+        <v>1.17320294972813</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,15 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.187180611507029</v>
+        <v>1.184347110058969</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B120">
+        <v>1.169611485058969</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187181970043989</v>
+        <v>1.187183995748591</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178878281123758</v>
+        <v>1.178881492958108</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177384541010027</v>
+        <v>1.177387340060094</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172927936128662</v>
+        <v>1.172931879979778</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171699934008554</v>
+        <v>1.171704063857678</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169680484324947</v>
+        <v>1.169684748553868</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167212642082881</v>
+        <v>1.167216942600961</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165471835821793</v>
+        <v>1.165476112992281</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166480733765293</v>
+        <v>1.166483656027713</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161094919596168</v>
+        <v>1.161094497541847</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161575806546584</v>
+        <v>1.161575540203835</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160925720518107</v>
+        <v>1.160925515454572</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162132989027633</v>
+        <v>1.162131442748956</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15974789501525</v>
+        <v>1.159747137054915</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415765987292</v>
+        <v>1.155415818218828</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148466319112513</v>
+        <v>1.148466810093146</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143141650865603</v>
+        <v>1.143141553637312</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137886526372916</v>
+        <v>1.137885309134571</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130159848433796</v>
+        <v>1.130156616897086</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125009216676208</v>
+        <v>1.125005141238527</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129851187759779</v>
+        <v>1.129842235450697</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136918894592068</v>
+        <v>1.136906179199339</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142902066667052</v>
+        <v>1.142880860940955</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146250753167858</v>
+        <v>1.146225995559162</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146124468196532</v>
+        <v>1.14609483704526</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140376965113386</v>
+        <v>1.140345961139314</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.13878877615123</v>
+        <v>1.138756189164791</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138661198322834</v>
+        <v>1.138626739236164</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150263040713353</v>
+        <v>1.150240389763045</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165758179324644</v>
+        <v>1.165743061932336</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166210573201054</v>
+        <v>1.166196417144131</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.18060691238498</v>
+        <v>1.180604578563003</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191519164827279</v>
+        <v>1.191530645478927</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199722843090615</v>
+        <v>1.199736698728272</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211445900883562</v>
+        <v>1.211466191795747</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205675815113205</v>
+        <v>1.205682664875842</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206460878346754</v>
+        <v>1.20647227937493</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.21010340363613</v>
+        <v>1.21012858616241</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215809843162684</v>
+        <v>1.215846464875312</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.221981073391731</v>
+        <v>1.22202331408003</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220668903441846</v>
+        <v>1.22070153152832</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20821625431845</v>
+        <v>1.208245541507771</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199927294209718</v>
+        <v>1.199954952075937</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189317396032939</v>
+        <v>1.189338263783849</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.180982498143994</v>
+        <v>1.181000040592874</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175774612397896</v>
+        <v>1.175787778139783</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172314353617138</v>
+        <v>1.172323191444056</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173586056652379</v>
+        <v>1.173600931722167</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169647181552147</v>
+        <v>1.169656711693259</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168416282280316</v>
+        <v>1.168427412134463</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168472318017013</v>
+        <v>1.168490165849921</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166368503372976</v>
+        <v>1.166383900262844</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.15814816626876</v>
+        <v>1.158159918335119</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151724207480517</v>
+        <v>1.151740853198368</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146162849649893</v>
+        <v>1.146179544506246</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143786989519702</v>
+        <v>1.143796100028461</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144583060924491</v>
+        <v>1.144579551558089</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146894404270362</v>
+        <v>1.14687976579875</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149841311181897</v>
+        <v>1.149811443124131</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151369157565837</v>
+        <v>1.151328665092775</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.15114240785387</v>
+        <v>1.151092835511527</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149132668417421</v>
+        <v>1.149544021794573</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.147349686989078</v>
+        <v>1.147854337335616</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.146510389227269</v>
+        <v>1.147034697587414</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.146228672599524</v>
+        <v>1.14674150850291</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.146074587701695</v>
+        <v>1.146562067619094</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.147265971250515</v>
+        <v>1.147702873320938</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.151874286677462</v>
+        <v>1.152208648803928</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.155207140750598</v>
+        <v>1.155504343244753</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.159298438555642</v>
+        <v>1.159536583321995</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.165578118736353</v>
+        <v>1.165642570861194</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.175613707871902</v>
+        <v>1.175260906905666</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.17320294972813</v>
+        <v>1.173046183829671</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.184347110058969</v>
+        <v>1.182860265137775</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.169611485058969</v>
+        <v>1.17003635045716</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187183995748591</v>
+        <v>1.187185979690574</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178881492958108</v>
+        <v>1.178884638751049</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177387340060094</v>
+        <v>1.177390082012948</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172931879979778</v>
+        <v>1.172935743171141</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171704063857678</v>
+        <v>1.171708109191848</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169684748553868</v>
+        <v>1.169688925470475</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167216942600961</v>
+        <v>1.167221155040806</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165476112992281</v>
+        <v>1.165480302560501</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166483656027713</v>
+        <v>1.166486519452903</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161094497541847</v>
+        <v>1.161094084492381</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161575540203835</v>
+        <v>1.161575279641337</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160925515454572</v>
+        <v>1.160925314900394</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162131442748956</v>
+        <v>1.16212992889937</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159747137054915</v>
+        <v>1.159746394926201</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415818218828</v>
+        <v>1.155415869795972</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148466810093146</v>
+        <v>1.148467292627098</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143141553637312</v>
+        <v>1.143141461207226</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137885309134571</v>
+        <v>1.137884121215728</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130156616897086</v>
+        <v>1.130153455396178</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125005141238527</v>
+        <v>1.125001152685196</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129842235450697</v>
+        <v>1.129833470995003</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136906179199339</v>
+        <v>1.136893729088777</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142880860940955</v>
+        <v>1.142860089408142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146225995559162</v>
+        <v>1.146201743086985</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.14609483704526</v>
+        <v>1.146065808920377</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140345961139314</v>
+        <v>1.140315584164286</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138756189164791</v>
+        <v>1.138724257378753</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138626739236164</v>
+        <v>1.138592968080354</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150240389763045</v>
+        <v>1.150218187176666</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165743061932336</v>
+        <v>1.165728244564067</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166196417144131</v>
+        <v>1.166182539311668</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180604578563003</v>
+        <v>1.180602288354072</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191530645478927</v>
+        <v>1.191541899511418</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199736698728272</v>
+        <v>1.199750279708211</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211466191795747</v>
+        <v>1.211486072402675</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205682664875842</v>
+        <v>1.205689357568657</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.20647227937493</v>
+        <v>1.206483427503032</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.21012858616241</v>
+        <v>1.210153240213482</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215846464875312</v>
+        <v>1.215882336055833</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.22202331408003</v>
+        <v>1.222064691782751</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.22070153152832</v>
+        <v>1.220733484751506</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208245541507771</v>
+        <v>1.208274227833656</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.199954952075937</v>
+        <v>1.19998204620862</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189338263783849</v>
+        <v>1.189358713237967</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181000040592874</v>
+        <v>1.181017233411192</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175787778139783</v>
+        <v>1.175800682755632</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172323191444056</v>
+        <v>1.172331853512004</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173600931722167</v>
+        <v>1.173615508572267</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169656711693259</v>
+        <v>1.169666045375769</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168427412134463</v>
+        <v>1.168438312144952</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168490165849921</v>
+        <v>1.168507651355342</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166383900262844</v>
+        <v>1.166398983126455</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158159918335119</v>
+        <v>1.158171423996829</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151740853198368</v>
+        <v>1.15175716778623</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146179544506246</v>
+        <v>1.146195919143839</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143796100028461</v>
+        <v>1.14380505664841</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144579551558089</v>
+        <v>1.144576152557331</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.14687976579875</v>
+        <v>1.146865449712119</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149811443124131</v>
+        <v>1.149782189637954</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151328665092775</v>
+        <v>1.151288957608086</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.151092835511527</v>
+        <v>1.151044172508351</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149544021794573</v>
+        <v>1.149838290280806</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.147854337335616</v>
+        <v>1.14822809250324</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.147034697587414</v>
+        <v>1.147406207832942</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.14674150850291</v>
+        <v>1.147128381052277</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.146562067619094</v>
+        <v>1.146896849636606</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.147702873320938</v>
+        <v>1.147978766115664</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.152208648803928</v>
+        <v>1.152368699112694</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.155504343244753</v>
+        <v>1.155607657805668</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.159536583321995</v>
+        <v>1.159569075261829</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.165642570861194</v>
+        <v>1.165503706585818</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.175260906905666</v>
+        <v>1.174711769848575</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.173046183829671</v>
+        <v>1.172617770320313</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.182860265137775</v>
+        <v>1.18123160970419</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.17003635045716</v>
+        <v>1.169665006808698</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187185979690574</v>
+        <v>1.187187923148204</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178884638751049</v>
+        <v>1.178887720518605</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177390082012948</v>
+        <v>1.177392768597636</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172935743171141</v>
+        <v>1.172939528151726</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171708109191848</v>
+        <v>1.171712072578643</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169688925470475</v>
+        <v>1.169693017728766</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167221155040806</v>
+        <v>1.167225282080394</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165480302560501</v>
+        <v>1.165484407190028</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166486519452903</v>
+        <v>1.166489325798748</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161094084492381</v>
+        <v>1.161093680162943</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161575279641337</v>
+        <v>1.161575024673381</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160925314900394</v>
+        <v>1.160925118708986</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.16212992889937</v>
+        <v>1.1621284464698</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159746394926201</v>
+        <v>1.159745668138567</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415869795972</v>
+        <v>1.155415920725737</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148467292627098</v>
+        <v>1.148467766921849</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143141461207226</v>
+        <v>1.143141373344015</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137884121215728</v>
+        <v>1.137882961592017</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130153455396178</v>
+        <v>1.130150361685518</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.125001152685196</v>
+        <v>1.124997248271922</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129833470995003</v>
+        <v>1.129824888548613</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136893729088777</v>
+        <v>1.13688153605448</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142860089408142</v>
+        <v>1.142839738880017</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146201743086985</v>
+        <v>1.146177980465618</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146065808920377</v>
+        <v>1.146037365624054</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140315584164286</v>
+        <v>1.140285815391636</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138724257378753</v>
+        <v>1.138692961271002</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138592968080354</v>
+        <v>1.138559864512315</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150218187176666</v>
+        <v>1.150196419802589</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165728244564067</v>
+        <v>1.165713718391128</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166182539311668</v>
+        <v>1.166168931601389</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180602288354072</v>
+        <v>1.180600040549746</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191541899511418</v>
+        <v>1.191552933554342</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199750279708211</v>
+        <v>1.199763594101261</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211486072402675</v>
+        <v>1.211505555013429</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205689357568657</v>
+        <v>1.205695898468883</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206483427503032</v>
+        <v>1.206494330993874</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210153240213482</v>
+        <v>1.210177382219018</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215882336055833</v>
+        <v>1.215917479517138</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222064691782751</v>
+        <v>1.222105232641113</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220733484751506</v>
+        <v>1.220764783803406</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208274227833656</v>
+        <v>1.208302331567133</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.19998204620862</v>
+        <v>1.200008593633002</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189358713237967</v>
+        <v>1.189378756815362</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181017233411192</v>
+        <v>1.181034086921296</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175800682755632</v>
+        <v>1.175813333923818</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172331853512004</v>
+        <v>1.172340345003049</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173615508572267</v>
+        <v>1.173629796065849</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169666045375769</v>
+        <v>1.169675188599222</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168438312144952</v>
+        <v>1.168448989343013</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168507651355342</v>
+        <v>1.16852478543847</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166398983126455</v>
+        <v>1.166413761463009</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158171423996829</v>
+        <v>1.158182690902039</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.15175716778623</v>
+        <v>1.15177316097562</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146195919143839</v>
+        <v>1.146211982604818</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14380505664841</v>
+        <v>1.143813863064052</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144576152557331</v>
+        <v>1.144572859494766</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146865449712119</v>
+        <v>1.146851445740522</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149782189637954</v>
+        <v>1.149753532296142</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151288957608086</v>
+        <v>1.151250013018876</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.151044172508351</v>
+        <v>1.15099639490636</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149838290280806</v>
+        <v>1.150058203727338</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.14822809250324</v>
+        <v>1.148516387164571</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.147406207832942</v>
+        <v>1.147681855126189</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.147128381052277</v>
+        <v>1.147381716040863</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.146896849636606</v>
+        <v>1.147094991043352</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.147978766115664</v>
+        <v>1.148094797200026</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.152368699112694</v>
+        <v>1.15234022581381</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.155607657805668</v>
+        <v>1.155484833581855</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.159569075261829</v>
+        <v>1.159341299139858</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.165503706585818</v>
+        <v>1.165028417068397</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.174711769848575</v>
+        <v>1.173766452416481</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.172617770320313</v>
+        <v>1.171626464841787</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.18123160970419</v>
+        <v>1.178933908368022</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.169665006808698</v>
+        <v>1.166806133005905</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187187923148204</v>
+        <v>1.187189827348111</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178887720518605</v>
+        <v>1.178890740195573</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177392768597636</v>
+        <v>1.177395401474105</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172939528151726</v>
+        <v>1.17294323727238</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171712072578643</v>
+        <v>1.171715956482697</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169693017728766</v>
+        <v>1.169697027876276</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167225282080394</v>
+        <v>1.167229326290246</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165484407190028</v>
+        <v>1.165488429437555</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166489325798748</v>
+        <v>1.166492076753854</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161093680162943</v>
+        <v>1.161093284280579</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161575024673381</v>
+        <v>1.161574775122116</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160925118708986</v>
+        <v>1.160924926740026</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.1621284464698</v>
+        <v>1.162126994492588</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159745668138567</v>
+        <v>1.159744956221515</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415920725737</v>
+        <v>1.155415971015378</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148467766921849</v>
+        <v>1.148468233178546</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143141373344015</v>
+        <v>1.143141289829064</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137882961592017</v>
+        <v>1.137881829285483</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130150361685518</v>
+        <v>1.130147333614282</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124997248271922</v>
+        <v>1.124993425368601</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129824888548613</v>
+        <v>1.129816482507081</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.13688153605448</v>
+        <v>1.136869592225133</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142839738880017</v>
+        <v>1.142819796696304</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146177980465618</v>
+        <v>1.14615469301922</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146037365624054</v>
+        <v>1.146009489682386</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140285815391636</v>
+        <v>1.140256636767289</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138692961271002</v>
+        <v>1.13866228208569</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138559864512315</v>
+        <v>1.138527408981058</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150196419802589</v>
+        <v>1.150175074997327</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165713718391128</v>
+        <v>1.165699474927247</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166168931601389</v>
+        <v>1.166155586221779</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180600040549746</v>
+        <v>1.18059783398573</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191552933554342</v>
+        <v>1.191563753981787</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199763594101261</v>
+        <v>1.199776649665733</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211505555013429</v>
+        <v>1.211524651450058</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205695898468883</v>
+        <v>1.205702292622238</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206494330993874</v>
+        <v>1.206504997756379</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210177382219018</v>
+        <v>1.210201027935932</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215917479517138</v>
+        <v>1.215951917157857</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222105232641113</v>
+        <v>1.222144961752582</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220764783803406</v>
+        <v>1.220795448539906</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208302331567133</v>
+        <v>1.208329870247166</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200008593633002</v>
+        <v>1.200034610697025</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189378756815362</v>
+        <v>1.189398406450521</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181034086921296</v>
+        <v>1.181050611044237</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175813333923818</v>
+        <v>1.175825739025155</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172340345003049</v>
+        <v>1.172348670897893</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173629796065849</v>
+        <v>1.173643802718946</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169675188599222</v>
+        <v>1.16968414712186</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168448989343013</v>
+        <v>1.168459450476594</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.16852478543847</v>
+        <v>1.168541578571904</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166413761463009</v>
+        <v>1.166428244392833</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158182690902039</v>
+        <v>1.158193726386434</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.15177316097562</v>
+        <v>1.151788842122524</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146211982604818</v>
+        <v>1.146227743597476</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143813863064052</v>
+        <v>1.143822522851622</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144572859494766</v>
+        <v>1.144569668159307</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146851445740522</v>
+        <v>1.146837744036248</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149753532296142</v>
+        <v>1.14972545338767</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151250013018876</v>
+        <v>1.151211810032996</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.15099639490636</v>
+        <v>1.150949479564944</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150058203727338</v>
+        <v>1.150269396327632</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148516387164571</v>
+        <v>1.148798784085386</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.147681855126189</v>
+        <v>1.147963734131071</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.147381716040863</v>
+        <v>1.147653551190573</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.147094991043352</v>
+        <v>1.147347026297663</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.148094797200026</v>
+        <v>1.148280269708015</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.15234022581381</v>
+        <v>1.152399955612526</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.155484833581855</v>
+        <v>1.155465509457261</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.159341299139858</v>
+        <v>1.159230037589284</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.165028417068397</v>
+        <v>1.16472459062983</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.173766452416481</v>
+        <v>1.173055522561268</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.171626464841787</v>
+        <v>1.170918786070935</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.178933908368022</v>
+        <v>1.177230256732042</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.166806133005905</v>
+        <v>1.165460749761567</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187189827348111</v>
+        <v>1.187191693467867</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178890740195573</v>
+        <v>1.17889369963958</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177395401474105</v>
+        <v>1.177397982236616</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.17294323727238</v>
+        <v>1.172946872790687</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171715956482697</v>
+        <v>1.171719763270807</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169697027876276</v>
+        <v>1.169700958359356</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167229326290246</v>
+        <v>1.167233290138762</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165488429437555</v>
+        <v>1.165492371758201</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166492076753854</v>
+        <v>1.166494773940923</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161093284280579</v>
+        <v>1.1610928965836</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161574775122116</v>
+        <v>1.161574530817131</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160924926740026</v>
+        <v>1.160924738859127</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162126994492588</v>
+        <v>1.16212557203939</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159744956221515</v>
+        <v>1.159744258723581</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155415971015378</v>
+        <v>1.155416020672362</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148468233178546</v>
+        <v>1.148468691592226</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143141289829064</v>
+        <v>1.143141210455668</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137881829285483</v>
+        <v>1.137880723362017</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130147333614282</v>
+        <v>1.130144369121437</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124993425368601</v>
+        <v>1.124989681453439</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129816482507081</v>
+        <v>1.129808247493457</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136869592225133</v>
+        <v>1.136857890047148</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142819796696304</v>
+        <v>1.14280025069888</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14615469301922</v>
+        <v>1.146131866651741</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.146009489682386</v>
+        <v>1.145982164309802</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140256636767289</v>
+        <v>1.14022803094351</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.13866228208569</v>
+        <v>1.138632201796093</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138527408981058</v>
+        <v>1.138495582689624</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150175074997327</v>
+        <v>1.150154140601293</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165699474927247</v>
+        <v>1.165685506012175</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166155586221779</v>
+        <v>1.166142495677362</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.18059783398573</v>
+        <v>1.180595667539884</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191563753981787</v>
+        <v>1.191574366924497</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199776649665733</v>
+        <v>1.199789453862365</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211524651450058</v>
+        <v>1.211543373071411</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205702292622238</v>
+        <v>1.205708544855381</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206504997756379</v>
+        <v>1.206515435364228</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210201027935932</v>
+        <v>1.210224192482399</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.215951917157857</v>
+        <v>1.21598567000765</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222144961752582</v>
+        <v>1.222183903222379</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220795448539906</v>
+        <v>1.220825498022525</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208329870247166</v>
+        <v>1.208356860716898</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200034610697025</v>
+        <v>1.200060113104614</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189398406450521</v>
+        <v>1.18941767361579</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181050611044237</v>
+        <v>1.18106681531903</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175825739025155</v>
+        <v>1.175837905157139</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172348670897893</v>
+        <v>1.172356835985547</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173643802718946</v>
+        <v>1.173657536717252</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.16968414712186</v>
+        <v>1.169692926472605</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168459450476594</v>
+        <v>1.168469702024459</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168541578571904</v>
+        <v>1.168558040816855</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166428244392833</v>
+        <v>1.166442440676058</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158193726386434</v>
+        <v>1.158204537488994</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151788842122524</v>
+        <v>1.151804220225232</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146227743597476</v>
+        <v>1.146243210511346</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143822522851622</v>
+        <v>1.143831039482524</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144569668159307</v>
+        <v>1.144566574543802</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146837744036248</v>
+        <v>1.146824335152771</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.14972545338767</v>
+        <v>1.14969793588388</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151211810032996</v>
+        <v>1.15117432812413</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150949479564944</v>
+        <v>1.150903404109818</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150269396327632</v>
+        <v>1.150487234745892</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148798784085386</v>
+        <v>1.149087770391659</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.147963734131071</v>
+        <v>1.148252084339329</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.147653551190573</v>
+        <v>1.147934075289466</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.147347026297663</v>
+        <v>1.147609015692525</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.148280269708015</v>
+        <v>1.148479613889182</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.152399955612526</v>
+        <v>1.152482141492807</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.155465509457261</v>
+        <v>1.155476937183306</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.159230037589284</v>
+        <v>1.159159720047053</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.16472459062983</v>
+        <v>1.164483690768523</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.173055522561268</v>
+        <v>1.172455634314912</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.170918786070935</v>
+        <v>1.170353179723362</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.177230256732042</v>
+        <v>1.175883080193089</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.165460749761567</v>
+        <v>1.164750190474933</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187191693467867</v>
+        <v>1.187193522638415</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.17889369963958</v>
+        <v>1.178896600634883</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177397982236616</v>
+        <v>1.177400512416966</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172946872790687</v>
+        <v>1.172950436875544</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171719763270807</v>
+        <v>1.17172349521674</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169700958359356</v>
+        <v>1.16970481152815</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167233290138762</v>
+        <v>1.167237175997242</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165492371758201</v>
+        <v>1.165496236510505</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166494773940923</v>
+        <v>1.166497418919929</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.1610928965836</v>
+        <v>1.161092516821003</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161574530817131</v>
+        <v>1.161574291595078</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160924738859127</v>
+        <v>1.16092455493753</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.16212557203939</v>
+        <v>1.162124178219195</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159744258723581</v>
+        <v>1.15974357521138</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416020672362</v>
+        <v>1.155416069704324</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148468691592226</v>
+        <v>1.148469142352016</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143141210455668</v>
+        <v>1.143141135028294</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137880723362017</v>
+        <v>1.137879642928958</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130144369121437</v>
+        <v>1.130141466231123</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124989681453439</v>
+        <v>1.124986014107453</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129808247493457</v>
+        <v>1.12980017834687</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136857890047148</v>
+        <v>1.136846422268803</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14280025069888</v>
+        <v>1.142781089207141</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146131866651741</v>
+        <v>1.146109487818596</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145982164309802</v>
+        <v>1.145955373375545</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.14022803094351</v>
+        <v>1.140199981244754</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138632201796093</v>
+        <v>1.138602703069593</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138495582689624</v>
+        <v>1.13846436755918</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150154140601293</v>
+        <v>1.150133604915923</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165685506012175</v>
+        <v>1.165671803796203</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166142495677362</v>
+        <v>1.166129652754816</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180595667539884</v>
+        <v>1.180593540130334</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191574366924497</v>
+        <v>1.191584778281354</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199789453862365</v>
+        <v>1.199802013868427</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211543373071411</v>
+        <v>1.211561730795578</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205708544855381</v>
+        <v>1.205714659787578</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206515435364228</v>
+        <v>1.20652565107334</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210224192482399</v>
+        <v>1.210246890369843</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.21598567000765</v>
+        <v>1.216018758269839</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222183903222379</v>
+        <v>1.222222080211961</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220825498022525</v>
+        <v>1.220854950557691</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208356860716898</v>
+        <v>1.208383319157758</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200060113104614</v>
+        <v>1.200085115947016</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.18941767361579</v>
+        <v>1.189436569343462</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.18106681531903</v>
+        <v>1.181082708920818</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175837905157139</v>
+        <v>1.175849839147392</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172356835985547</v>
+        <v>1.172364844872447</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173657536717252</v>
+        <v>1.173671005931958</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169692926472605</v>
+        <v>1.169701531962345</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168469702024459</v>
+        <v>1.168479750209447</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168558040816855</v>
+        <v>1.168574181843119</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166442440676058</v>
+        <v>1.166456358730212</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158204537488994</v>
+        <v>1.158215130966806</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151804220225232</v>
+        <v>1.151819303941173</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146243210511346</v>
+        <v>1.146258391431494</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143831039482524</v>
+        <v>1.143839416326686</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144566574543802</v>
+        <v>1.144563574833411</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146824335152771</v>
+        <v>1.146811210024921</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.14969793588388</v>
+        <v>1.149670963406518</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.15117432812413</v>
+        <v>1.151137547498627</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150903404109818</v>
+        <v>1.150858146903301</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150487234745892</v>
+        <v>1.15043423635252</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.149087770391659</v>
+        <v>1.149170563066065</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.148252084339329</v>
+        <v>1.148264861758078</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.147934075289466</v>
+        <v>1.147860885518038</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.147609015692525</v>
+        <v>1.147283752084409</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.148479613889182</v>
+        <v>1.14794717947303</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.152482141492807</v>
+        <v>1.151603101574697</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.155476937183306</v>
+        <v>1.154249903168665</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.159159720047053</v>
+        <v>1.157555556005161</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.164483690768523</v>
+        <v>1.162319464011275</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.172455634314912</v>
+        <v>1.169035513198729</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.170353179723362</v>
+        <v>1.165998057515874</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.175883080193089</v>
+        <v>1.169131560732178</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,15 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.164750190474933</v>
+        <v>1.153025880380417</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B121">
+        <v>1.139381505380417</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187193522638415</v>
+        <v>1.187195315946355</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178896600634883</v>
+        <v>1.178899444895964</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177400512416966</v>
+        <v>1.177402993487514</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172950436875544</v>
+        <v>1.172953931611477</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.17172349521674</v>
+        <v>1.17172715450576</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.16970481152815</v>
+        <v>1.169708589641278</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167237175997242</v>
+        <v>1.167240986144614</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165496236510505</v>
+        <v>1.165500025961129</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166497418919929</v>
+        <v>1.166500013191127</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161092516821003</v>
+        <v>1.161092144751936</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161574291595078</v>
+        <v>1.161574057299305</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.16092455493753</v>
+        <v>1.160924374851807</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162124178219195</v>
+        <v>1.162122812176477</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15974357521138</v>
+        <v>1.159742905268715</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416069704324</v>
+        <v>1.155416118119043</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148469142352016</v>
+        <v>1.148469585641338</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143141135028294</v>
+        <v>1.143141063361882</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137879642928958</v>
+        <v>1.137878587132845</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130141466231123</v>
+        <v>1.130138623048304</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124986014107453</v>
+        <v>1.124982421009281</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.12980017834687</v>
+        <v>1.129792270111792</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136846422268803</v>
+        <v>1.136835181925339</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142781089207141</v>
+        <v>1.14276230099481</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146109487818596</v>
+        <v>1.146087543499997</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145955373375545</v>
+        <v>1.145929101372093</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140199981244754</v>
+        <v>1.140172471635478</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138602703069593</v>
+        <v>1.138573769234664</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.13846436755918</v>
+        <v>1.138433746195136</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150133604915923</v>
+        <v>1.15011345668209</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165671803796203</v>
+        <v>1.16565836072556</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166129652754816</v>
+        <v>1.166117050509851</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180593540130334</v>
+        <v>1.180591450713686</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191584778281354</v>
+        <v>1.191594993730206</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199802013868427</v>
+        <v>1.199814336591036</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211561730795578</v>
+        <v>1.21157973512105</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205714659787578</v>
+        <v>1.205720641841637</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.20652565107334</v>
+        <v>1.206535651838284</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210246890369843</v>
+        <v>1.210269135533022</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216018758269839</v>
+        <v>1.216051201361564</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222222080211961</v>
+        <v>1.222259514984704</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220854950557691</v>
+        <v>1.220883823733712</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208383319157758</v>
+        <v>1.208409261121585</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200085115947016</v>
+        <v>1.20010963373233</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189436569343462</v>
+        <v>1.189455104246626</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181082708920818</v>
+        <v>1.181098300678013</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175849839147392</v>
+        <v>1.17586154756634</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172364844872447</v>
+        <v>1.172372701991055</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173671005931958</v>
+        <v>1.173684217934686</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169701531962345</v>
+        <v>1.169709968694545</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168479750209447</v>
+        <v>1.168489601010961</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168574181843119</v>
+        <v>1.168590010947896</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166456358730212</v>
+        <v>1.166470006646785</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158215130966806</v>
+        <v>1.158225513309</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151819303941173</v>
+        <v>1.151834101602812</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146258391431494</v>
+        <v>1.146273294152058</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143839416326686</v>
+        <v>1.143847656655817</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144563574833411</v>
+        <v>1.144560665394746</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146811210024921</v>
+        <v>1.146798359950194</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149670963406518</v>
+        <v>1.149644520197512</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151137547498627</v>
+        <v>1.151101449063991</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150858146903301</v>
+        <v>1.150813687015839</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.15043423635252</v>
+        <v>1.150382131581888</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.149170563066065</v>
+        <v>1.149239190243257</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.148264861758078</v>
+        <v>1.148261425810852</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.147860885518038</v>
+        <v>1.147769847848727</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.147283752084409</v>
+        <v>1.1469424341708</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.14794717947303</v>
+        <v>1.147409547152442</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.151603101574697</v>
+        <v>1.15073320587985</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.154249903168665</v>
+        <v>1.153050013368306</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.157555556005161</v>
+        <v>1.156000808554071</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.162319464011275</v>
+        <v>1.160246820586966</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.169035513198729</v>
+        <v>1.165814936130506</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.165998057515874</v>
+        <v>1.16198414539402</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.169131560732178</v>
+        <v>1.163174327962677</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.153025880380417</v>
+        <v>1.144022360166686</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.139381505380417</v>
+        <v>1.130377985166686</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.149239190243257</v>
+        <v>1.14906047621223</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.148261425810852</v>
+        <v>1.148036963123568</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.147769847848727</v>
+        <v>1.147509557803832</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.1469424341708</v>
+        <v>1.146615842867536</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.147409547152442</v>
+        <v>1.147078953300831</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.15073320587985</v>
+        <v>1.150355759044595</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.153050013368306</v>
+        <v>1.152614444082088</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.156000808554071</v>
+        <v>1.155509517337534</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.160246820586966</v>
+        <v>1.15966397703187</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.165814936130506</v>
+        <v>1.165070424376734</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.16198414539402</v>
+        <v>1.161034615481407</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.163174327962677</v>
+        <v>1.161867483086974</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.144022360166686</v>
+        <v>1.141644883461886</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.130377985166686</v>
+        <v>1.126909258461886</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187195315946355</v>
+        <v>1.187197074436097</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178899444895964</v>
+        <v>1.178902234070903</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177402993487514</v>
+        <v>1.177405426864034</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172953931611477</v>
+        <v>1.1729573590027</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.17172715450576</v>
+        <v>1.17173074323889</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169708589641278</v>
+        <v>1.169712294870244</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167240986144614</v>
+        <v>1.167244722771889</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165500025961129</v>
+        <v>1.165503742289288</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166500013191127</v>
+        <v>1.166502558197875</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161092144751936</v>
+        <v>1.161091780145187</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161574057299305</v>
+        <v>1.161573827779522</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160924374851807</v>
+        <v>1.160924198483595</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162122812176477</v>
+        <v>1.162121473089439</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159742905268715</v>
+        <v>1.159742248495726</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416118119043</v>
+        <v>1.155416165924406</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148469585641338</v>
+        <v>1.148470021638101</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143141063361882</v>
+        <v>1.143140995281204</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137878587132845</v>
+        <v>1.137877555157318</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130138623048304</v>
+        <v>1.130135837754688</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124982421009281</v>
+        <v>1.124978899930321</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129792270111792</v>
+        <v>1.129784518027941</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136835181925339</v>
+        <v>1.136824162324911</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14276230099481</v>
+        <v>1.142743875268073</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146087543499997</v>
+        <v>1.146066021175802</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145929101372093</v>
+        <v>1.145903333385388</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140172471635478</v>
+        <v>1.140145486689781</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138573769234664</v>
+        <v>1.138545384249711</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138433746195136</v>
+        <v>1.138403701855171</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.15011345668209</v>
+        <v>1.150093685059702</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.16565836072556</v>
+        <v>1.165645169528614</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166117050509851</v>
+        <v>1.166104682254819</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180591450713686</v>
+        <v>1.180589398283328</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191594993730206</v>
+        <v>1.191605018738106</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199814336591036</v>
+        <v>1.199826428679716</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.21157973512105</v>
+        <v>1.211597396146662</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205720641841637</v>
+        <v>1.205726495254164</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206535651838284</v>
+        <v>1.206545444327679</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210269135533022</v>
+        <v>1.210290941358334</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216051201361564</v>
+        <v>1.21608301795161</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222259514984704</v>
+        <v>1.222296228948954</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220883823733712</v>
+        <v>1.220912134455596</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208409261121585</v>
+        <v>1.208434701560908</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.20010963373233</v>
+        <v>1.200133680413349</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189455104246626</v>
+        <v>1.189473288538838</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181098300678013</v>
+        <v>1.18111359908848</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.17586154756634</v>
+        <v>1.175873036739195</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172372701991055</v>
+        <v>1.172380411607982</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173684217934686</v>
+        <v>1.173697180011581</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169709968694545</v>
+        <v>1.169718241575264</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168489601010961</v>
+        <v>1.168499260176731</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168590010947896</v>
+        <v>1.168605537073544</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166470006646785</v>
+        <v>1.166483392206849</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158225513309</v>
+        <v>1.158235690749874</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151834101602812</v>
+        <v>1.151848621232678</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146273294152058</v>
+        <v>1.146287926189083</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143847656655817</v>
+        <v>1.143855763646571</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144560665394746</v>
+        <v>1.144557842765715</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146798359950194</v>
+        <v>1.146785776571141</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149644520197512</v>
+        <v>1.149618591090392</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151101449063991</v>
+        <v>1.151066014398924</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150813687015839</v>
+        <v>1.150770004198752</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150382131581888</v>
+        <v>1.150330899018618</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.14906047621223</v>
+        <v>1.148922045747999</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.148036963123568</v>
+        <v>1.147777746250566</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.147509557803832</v>
+        <v>1.147126824673597</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.146615842867536</v>
+        <v>1.145914207516221</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.147078953300831</v>
+        <v>1.146184731518421</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.150355759044595</v>
+        <v>1.149091507047448</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.152614444082088</v>
+        <v>1.150972602812893</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.155509517337534</v>
+        <v>1.153471034870272</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.15966397703187</v>
+        <v>1.157047055040938</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.165070424376734</v>
+        <v>1.161228943880023</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.161034615481407</v>
+        <v>1.156311092890628</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.161867483086974</v>
+        <v>1.155214956340513</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.141644883461886</v>
+        <v>1.132253425522068</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.126909258461886</v>
+        <v>1.066901056828268</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187197074436097</v>
+        <v>1.187198799111886</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178902234070903</v>
+        <v>1.178904969744563</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177405426864034</v>
+        <v>1.177407813908411</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.1729573590027</v>
+        <v>1.172960720976947</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.17173074323889</v>
+        <v>1.171734263436933</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169712294870244</v>
+        <v>1.169715929303599</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167244722771889</v>
+        <v>1.167248387986354</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165503742289288</v>
+        <v>1.165507387590924</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166502558197875</v>
+        <v>1.166505055329303</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161091780145187</v>
+        <v>1.161091422778708</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161573827779522</v>
+        <v>1.161573602891474</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160924198483595</v>
+        <v>1.160924025719335</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162121473089439</v>
+        <v>1.16212016016837</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159742248495726</v>
+        <v>1.159741604508103</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416165924406</v>
+        <v>1.155416213128391</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148470021638101</v>
+        <v>1.148470450514892</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140995281204</v>
+        <v>1.14314093062027</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137877555157318</v>
+        <v>1.137876546221143</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130135837754688</v>
+        <v>1.130133108604886</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124978899930321</v>
+        <v>1.124975448730147</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129784518027941</v>
+        <v>1.129776917520765</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136824162324911</v>
+        <v>1.136813357035368</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142743875268073</v>
+        <v>1.142725801644976</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146066021175802</v>
+        <v>1.146044908801798</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145903333385388</v>
+        <v>1.145878055066747</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140145486689781</v>
+        <v>1.140119011562751</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138545384249711</v>
+        <v>1.13851753267366</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138403701855171</v>
+        <v>1.138374218419012</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150093685059702</v>
+        <v>1.150074279608443</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165645169528614</v>
+        <v>1.165632223202846</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166104682254819</v>
+        <v>1.166092541546988</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180589398283328</v>
+        <v>1.180587381867835</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191605018738106</v>
+        <v>1.191614858570976</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199826428679716</v>
+        <v>1.199838296538278</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211597396146662</v>
+        <v>1.211614723590417</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205726495254164</v>
+        <v>1.205732224085181</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206545444327679</v>
+        <v>1.20655503493867</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210290941358334</v>
+        <v>1.210312320710492</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.21608301795161</v>
+        <v>1.216114225996085</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222296228948954</v>
+        <v>1.222332242698625</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220912134455596</v>
+        <v>1.220939898977874</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208434701560908</v>
+        <v>1.208459654857489</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200133680413349</v>
+        <v>1.200157269413825</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189473288538838</v>
+        <v>1.189491132052696</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.18111359908848</v>
+        <v>1.181128612334823</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175873036739195</v>
+        <v>1.175884312757265</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172380411607982</v>
+        <v>1.172387977831659</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173697180011581</v>
+        <v>1.173709899176613</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169718241575264</v>
+        <v>1.169726355322586</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168499260176731</v>
+        <v>1.168508733233911</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168605537073544</v>
+        <v>1.16862076882432</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166483392206849</v>
+        <v>1.166496522895786</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158235690749874</v>
+        <v>1.158245669281249</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151848621232678</v>
+        <v>1.151862870557558</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146287926189083</v>
+        <v>1.146302294792687</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143855763646571</v>
+        <v>1.14386374038362</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144557842765715</v>
+        <v>1.14455510364602</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146785776571141</v>
+        <v>1.146773451858743</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149618591090392</v>
+        <v>1.149593161483247</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151066014398924</v>
+        <v>1.151031225724845</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150770004198752</v>
+        <v>1.150727078858129</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150330899018618</v>
+        <v>1.150280517885917</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148922045747999</v>
+        <v>1.148791100528209</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.147777746250566</v>
+        <v>1.147535904688657</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.147126824673597</v>
+        <v>1.146792825046481</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.145914207516221</v>
+        <v>1.145358212559668</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.146184731518421</v>
+        <v>1.145485085336112</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.149091507047448</v>
+        <v>1.148119501343339</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.150972602812893</v>
+        <v>1.149737741273017</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.153471034870272</v>
+        <v>1.15195768653543</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.157047055040938</v>
+        <v>1.155119355105867</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.161228943880023</v>
+        <v>1.158456147293517</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.156311092890628</v>
+        <v>1.153009523577246</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.155214956340513</v>
+        <v>1.150672092795011</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.132253425522068</v>
+        <v>1.12687505171266</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.066901056828268</v>
+        <v>1.069426182330334</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187198799111886</v>
+        <v>1.187200490939715</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178904969744563</v>
+        <v>1.178907653441591</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177407813908411</v>
+        <v>1.177410155931178</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172960720976947</v>
+        <v>1.172964019389085</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171734263436933</v>
+        <v>1.171737717044261</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169715929303599</v>
+        <v>1.169719494950863</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167248387986354</v>
+        <v>1.167251983815541</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165507387590924</v>
+        <v>1.165510963882646</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166505055329303</v>
+        <v>1.166507505922842</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161091422778708</v>
+        <v>1.161091072439168</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161573602891474</v>
+        <v>1.161573382496652</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160924025719335</v>
+        <v>1.160923856450036</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.16212016016837</v>
+        <v>1.162118872654098</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159741604508103</v>
+        <v>1.159740972936336</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416213128391</v>
+        <v>1.155416259739037</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148470450514892</v>
+        <v>1.148470872439156</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14314093062027</v>
+        <v>1.143140869221765</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137876546221143</v>
+        <v>1.137875559576368</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130133108604886</v>
+        <v>1.130130433922811</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124975448730147</v>
+        <v>1.124972065352198</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129776917520765</v>
+        <v>1.129769464192484</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136813357035368</v>
+        <v>1.136802759871788</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142725801644976</v>
+        <v>1.142708070135975</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146044908801798</v>
+        <v>1.14602419478733</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145878055066747</v>
+        <v>1.145853252606359</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140119011562751</v>
+        <v>1.140093031963409</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.13851753267366</v>
+        <v>1.138490199638175</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138374218419012</v>
+        <v>1.13834528035989</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150074279608443</v>
+        <v>1.150055230269545</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165632223202846</v>
+        <v>1.165619515002535</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166092541546988</v>
+        <v>1.16608062217747</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180587381867835</v>
+        <v>1.180585400529439</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191614858570976</v>
+        <v>1.19162451830276</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199838296538278</v>
+        <v>1.19984994633604</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211614723590417</v>
+        <v>1.211631726807257</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205732224085181</v>
+        <v>1.205737832227166</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.20655503493867</v>
+        <v>1.206564429810535</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210312320710492</v>
+        <v>1.210333285957643</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216114225996085</v>
+        <v>1.216144842772069</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222332242698625</v>
+        <v>1.222367576051522</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220939898977874</v>
+        <v>1.220967132935547</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208459654857489</v>
+        <v>1.208484134849261</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200157269413825</v>
+        <v>1.200180413653256</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189491132052696</v>
+        <v>1.189508644257401</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181128612334823</v>
+        <v>1.181143348298838</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175884312757265</v>
+        <v>1.17589538148865</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172387977831659</v>
+        <v>1.172395404619589</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173709899176613</v>
+        <v>1.173722382184155</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169726355322586</v>
+        <v>1.16973431447552</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168508733233911</v>
+        <v>1.168518025499532</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.16862076882432</v>
+        <v>1.168635714482187</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166496522895786</v>
+        <v>1.166509405917187</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158245669281249</v>
+        <v>1.158255454664122</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151862870557558</v>
+        <v>1.151876857021934</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146302294792687</v>
+        <v>1.146316406958602</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14386374038362</v>
+        <v>1.143871589862633</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.14455510364602</v>
+        <v>1.144552444888253</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146773451858743</v>
+        <v>1.146761378096731</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149593161483247</v>
+        <v>1.14956821731313</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.151031225724845</v>
+        <v>1.150997065878805</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150727078858129</v>
+        <v>1.150684892029834</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150280517885917</v>
+        <v>1.150230968024042</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148791100528209</v>
+        <v>1.148734371530398</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.147535904688657</v>
+        <v>1.147386373286576</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.146792825046481</v>
+        <v>1.146562733091418</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.145358212559668</v>
+        <v>1.144957581996374</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.145485085336112</v>
+        <v>1.144928375676128</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.148119501343339</v>
+        <v>1.147319325464565</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.149737741273017</v>
+        <v>1.148710213021927</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.15195768653543</v>
+        <v>1.150688945230954</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.155119355105867</v>
+        <v>1.153500430008125</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.158456147293517</v>
+        <v>1.156117356330579</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.153009523577246</v>
+        <v>1.150288839521377</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.150672092795011</v>
+        <v>1.147033057252961</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.12687505171266</v>
+        <v>1.1231018238173</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.069426182330334</v>
+        <v>1.072288397627613</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B121"/>
+  <dimension ref="A1:B122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187200490939715</v>
+        <v>1.187202150849132</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178907653441591</v>
+        <v>1.178910286629253</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177410155931178</v>
+        <v>1.177412454193913</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172964019389085</v>
+        <v>1.172967256024523</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171737717044261</v>
+        <v>1.171741105932398</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169719494950863</v>
+        <v>1.169722993746227</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167251983815541</v>
+        <v>1.167255512210954</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165510963882646</v>
+        <v>1.165514473105451</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166507505922842</v>
+        <v>1.166509911266595</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161091072439168</v>
+        <v>1.161090728921524</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161573382496652</v>
+        <v>1.161573166462001</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160923856450036</v>
+        <v>1.160923690571042</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162118872654098</v>
+        <v>1.162117609816524</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159740972936336</v>
+        <v>1.15974035342501</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416259739037</v>
+        <v>1.155416305764428</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148470872439156</v>
+        <v>1.148471287573368</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140869221765</v>
+        <v>1.143140810936534</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137875559576368</v>
+        <v>1.137874594506591</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130130433922811</v>
+        <v>1.13012781209827</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124972065352198</v>
+        <v>1.124968747819715</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129769464192484</v>
+        <v>1.129762153813638</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136802759871788</v>
+        <v>1.136792364884729</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142708070135975</v>
+        <v>1.142690671125589</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14602419478733</v>
+        <v>1.146003867974164</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145853252606359</v>
+        <v>1.145828912708254</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140093031963409</v>
+        <v>1.140067534129157</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138490199638175</v>
+        <v>1.138463370821393</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.13834528035989</v>
+        <v>1.138316872717541</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150055230269545</v>
+        <v>1.150036527348559</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165619515002535</v>
+        <v>1.16560703842711</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.16608062217747</v>
+        <v>1.166068918160724</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180585400529439</v>
+        <v>1.180583453362589</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.19162451830276</v>
+        <v>1.19163400282407</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.19984994633604</v>
+        <v>1.19986138401845</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211631726807257</v>
+        <v>1.211648414805846</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205737832227166</v>
+        <v>1.205743323413542</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206564429810535</v>
+        <v>1.206573634837484</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210333285957643</v>
+        <v>1.210353848995065</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216144842772069</v>
+        <v>1.216174884909386</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222367576051522</v>
+        <v>1.222402248085503</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220967132935547</v>
+        <v>1.220993851373284</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208484134849261</v>
+        <v>1.208508154855752</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200180413653256</v>
+        <v>1.200203125570306</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189508644257401</v>
+        <v>1.189525834275344</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181143348298838</v>
+        <v>1.181157814575168</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.17589538148865</v>
+        <v>1.175906248588357</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172395404619589</v>
+        <v>1.172402695785202</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173722382184155</v>
+        <v>1.173734635540857</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.16973431447552</v>
+        <v>1.169742123402403</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168518025499532</v>
+        <v>1.168527142090378</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168635714482187</v>
+        <v>1.168650382021743</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166509405917187</v>
+        <v>1.166522048205978</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158255454664122</v>
+        <v>1.158265052439647</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151876857021934</v>
+        <v>1.151890587800692</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146316406958602</v>
+        <v>1.146330269439129</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143871589862633</v>
+        <v>1.14387931499316</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144552444888253</v>
+        <v>1.144549863489562</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146761378096731</v>
+        <v>1.146749547866773</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.14956821731313</v>
+        <v>1.149543745031815</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150997065878805</v>
+        <v>1.150963518287714</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150684892029834</v>
+        <v>1.150643425355568</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150230968024042</v>
+        <v>1.150182229869502</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148734371530398</v>
+        <v>1.148685234482818</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.147386373286576</v>
+        <v>1.147318770645895</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.146562733091418</v>
+        <v>1.146465567581281</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.144957581996374</v>
+        <v>1.144842898962162</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.144928375676128</v>
+        <v>1.144585924646217</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.147319325464565</v>
+        <v>1.146830095729518</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.148710213021927</v>
+        <v>1.148076894254769</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.150688945230954</v>
+        <v>1.149901698658863</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.153500430008125</v>
+        <v>1.152486104940667</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.156117356330579</v>
+        <v>1.154799640405493</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.150288839521377</v>
+        <v>1.148719437727565</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.147033057252961</v>
+        <v>1.145029796220284</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.1231018238173</v>
+        <v>1.12193452061355</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,15 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.072288397627613</v>
+        <v>1.07817927938096</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B122">
+        <v>1.09291490438096</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187202150849132</v>
+        <v>1.187203779734941</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178910286629253</v>
+        <v>1.178912870720106</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177412454193913</v>
+        <v>1.177414709911502</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172967256024523</v>
+        <v>1.172970432602433</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171741105932398</v>
+        <v>1.171744431903398</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169722993746227</v>
+        <v>1.169726427552048</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167255512210954</v>
+        <v>1.167258975051608</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165514473105451</v>
+        <v>1.165517917128229</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166509911266595</v>
+        <v>1.166512272601597</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161090728921524</v>
+        <v>1.161090392028631</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161573166462001</v>
+        <v>1.161572954659661</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160923690571042</v>
+        <v>1.160923527981826</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162117609816524</v>
+        <v>1.162116370953246</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15974035342501</v>
+        <v>1.159739745632139</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416305764428</v>
+        <v>1.155416351212673</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148471287573368</v>
+        <v>1.14847169607521</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140810936534</v>
+        <v>1.143140755623095</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137874594506591</v>
+        <v>1.137873650325331</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.13012781209827</v>
+        <v>1.130125241583773</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124968747819715</v>
+        <v>1.12496549423191</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129762153813638</v>
+        <v>1.129754982315119</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136792364884729</v>
+        <v>1.136782166349131</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142690671125589</v>
+        <v>1.142673595355062</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.146003867974164</v>
+        <v>1.145983917616537</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145828912708254</v>
+        <v>1.145805022566652</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140067534129157</v>
+        <v>1.140042504801614</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138463370821393</v>
+        <v>1.1384370324231</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138316872717541</v>
+        <v>1.138288981072663</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150036527348559</v>
+        <v>1.150018161499043</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.16560703842711</v>
+        <v>1.16559478721013</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166068918160724</v>
+        <v>1.166057423724629</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180583453362589</v>
+        <v>1.180581539492582</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.19163400282407</v>
+        <v>1.191643316850376</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.19986138401845</v>
+        <v>1.199872615317127</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211648414805846</v>
+        <v>1.211664796264429</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205743323413542</v>
+        <v>1.205748701226657</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206573634837484</v>
+        <v>1.206582655680709</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210353848995065</v>
+        <v>1.21037402126751</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216174884909386</v>
+        <v>1.216204368420597</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222402248085503</v>
+        <v>1.222436277172664</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.220993851373284</v>
+        <v>1.221020068772989</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208508154855752</v>
+        <v>1.208531727702097</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200203125570306</v>
+        <v>1.200225417144921</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189525834275344</v>
+        <v>1.189542710897806</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181157814575168</v>
+        <v>1.181172018484244</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175906248588357</v>
+        <v>1.175916919507868</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172402695785202</v>
+        <v>1.172409855004342</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173734635540857</v>
+        <v>1.173746665516883</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169742123402403</v>
+        <v>1.169749786308827</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168527142090378</v>
+        <v>1.168536087932309</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168650382021743</v>
+        <v>1.16866477912433</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166522048205978</v>
+        <v>1.166534456440812</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158265052439647</v>
+        <v>1.158274467939501</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151890587800692</v>
+        <v>1.15190406981116</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146330269439129</v>
+        <v>1.146343888753531</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14387931499316</v>
+        <v>1.14388691860143</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144549863489562</v>
+        <v>1.144547356583835</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146749547866773</v>
+        <v>1.146737954034486</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149543745031815</v>
+        <v>1.14951973158283</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150963518287714</v>
+        <v>1.15093056694382</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150643425355568</v>
+        <v>1.150602661059946</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150182229869502</v>
+        <v>1.150134284434962</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148685234482818</v>
+        <v>1.148636836919007</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.147318770645895</v>
+        <v>1.147110801071641</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.146465567581281</v>
+        <v>1.146206054994339</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.144842898962162</v>
+        <v>1.144543735760726</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.144585924646217</v>
+        <v>1.144039160632087</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.146830095729518</v>
+        <v>1.146107766014591</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.148076894254769</v>
+        <v>1.14717045593943</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.149901698658863</v>
+        <v>1.14880149673196</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.152486104940667</v>
+        <v>1.151102476714264</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.154799640405493</v>
+        <v>1.153046558474409</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.148719437727565</v>
+        <v>1.146579335300756</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.145029796220284</v>
+        <v>1.142322199916399</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.12193452061355</v>
+        <v>1.119568385966485</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.07817927938096</v>
+        <v>1.079850173796703</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.09291490438096</v>
+        <v>1.091137441095609</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187203779734941</v>
+        <v>1.187205378458809</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178912870720106</v>
+        <v>1.178915407074524</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177414709911502</v>
+        <v>1.177416924254283</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172970432602433</v>
+        <v>1.172973550778793</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171744431903398</v>
+        <v>1.171747696693036</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169726427552048</v>
+        <v>1.169729798162157</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167258975051608</v>
+        <v>1.167262374147361</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165517917128229</v>
+        <v>1.165521297751086</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166512272601597</v>
+        <v>1.166514591123941</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161090392028631</v>
+        <v>1.161090061570858</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161572954659661</v>
+        <v>1.161572746966711</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160923527981826</v>
+        <v>1.160923368585783</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162116370953246</v>
+        <v>1.16211515538826</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159739745632139</v>
+        <v>1.159739149228538</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416351212673</v>
+        <v>1.155416396091891</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.14847169607521</v>
+        <v>1.148472098097726</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140755623095</v>
+        <v>1.143140703147194</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137873650325331</v>
+        <v>1.1378727263745</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130125241583773</v>
+        <v>1.13012272089151</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.12496549423191</v>
+        <v>1.124962302760363</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129754982315119</v>
+        <v>1.129747945780653</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136782166349131</v>
+        <v>1.136772158753857</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142673595355062</v>
+        <v>1.142656833905989</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145983917616537</v>
+        <v>1.14596433336228</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145805022566652</v>
+        <v>1.145781569843606</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140042504801614</v>
+        <v>1.140017931203771</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.1384370324231</v>
+        <v>1.138411171141235</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138288981072663</v>
+        <v>1.138261591522742</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150018161499043</v>
+        <v>1.150000123707117</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.16559478721013</v>
+        <v>1.165582755308856</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166057423724629</v>
+        <v>1.166046133301077</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180581539492582</v>
+        <v>1.180579658074264</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191643316850376</v>
+        <v>1.191652464929763</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199872615317127</v>
+        <v>1.199883645759371</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211664796264429</v>
+        <v>1.211680879545839</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205748701226657</v>
+        <v>1.205753969105298</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206582655680709</v>
+        <v>1.206591497779732</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.21037402126751</v>
+        <v>1.210393813790303</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216204368420597</v>
+        <v>1.216233308729353</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222436277172664</v>
+        <v>1.222469681011627</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221020068772989</v>
+        <v>1.221045799079838</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208531727702097</v>
+        <v>1.208554865741735</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200225417144921</v>
+        <v>1.200247299919249</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189542710897806</v>
+        <v>1.189559282599812</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181172018484244</v>
+        <v>1.18118596708451</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175916919507868</v>
+        <v>1.175927399504199</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172409855004342</v>
+        <v>1.172416885821405</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173746665516883</v>
+        <v>1.173758478156541</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169749786308827</v>
+        <v>1.16975730724514</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168536087932309</v>
+        <v>1.168544867769064</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.16866477912433</v>
+        <v>1.168678913191375</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166534456440812</v>
+        <v>1.166546637055793</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158274467939501</v>
+        <v>1.158283706295667</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.15190406981116</v>
+        <v>1.151917309724499</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146343888753531</v>
+        <v>1.146357271197913</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14388691860143</v>
+        <v>1.143894403433061</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144547356583835</v>
+        <v>1.144544921434365</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146737954034486</v>
+        <v>1.146726589736214</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.14951973158283</v>
+        <v>1.14949616437969</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.15093056694382</v>
+        <v>1.150898196381367</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150602661059946</v>
+        <v>1.150562581928539</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150134284434962</v>
+        <v>1.150087113289847</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148636836919007</v>
+        <v>1.148589163460801</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.147110801071641</v>
+        <v>1.146800695732576</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.146206054994339</v>
+        <v>1.145823201662862</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.144543735760726</v>
+        <v>1.144096707565605</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.144039160632087</v>
+        <v>1.143399333292739</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.146107766014591</v>
+        <v>1.145250561282714</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.14717045593943</v>
+        <v>1.146093369305293</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.14880149673196</v>
+        <v>1.147496286623899</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.151102476714264</v>
+        <v>1.149475255192349</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.153046558474409</v>
+        <v>1.151009429119355</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.146579335300756</v>
+        <v>1.144075024857068</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.142322199916399</v>
+        <v>1.139191352728517</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.119568385966485</v>
+        <v>1.116524128784161</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.079850173796703</v>
+        <v>1.07933515774562</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.091137441095609</v>
+        <v>1.083494028247831</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187205378458809</v>
+        <v>1.187206947850786</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178915407074524</v>
+        <v>1.178917897003089</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177416924254283</v>
+        <v>1.177419098350066</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172973550778793</v>
+        <v>1.172976612149266</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171747696693036</v>
+        <v>1.171750901973831</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169729798162157</v>
+        <v>1.169733107304978</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167262374147361</v>
+        <v>1.167265711242061</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165521297751086</v>
+        <v>1.165524616708472</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166514591123941</v>
+        <v>1.166516867986789</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161090061570858</v>
+        <v>1.161089737365738</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161572746966711</v>
+        <v>1.161572543264938</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160923368585783</v>
+        <v>1.160923212290043</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.16211515538826</v>
+        <v>1.162113962470726</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159739149228538</v>
+        <v>1.159738563897231</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416396091891</v>
+        <v>1.155416440410191</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148472098097726</v>
+        <v>1.148472493789484</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140703147194</v>
+        <v>1.143140653381375</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.1378727263745</v>
+        <v>1.137871822022971</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.13012272089151</v>
+        <v>1.130120248590511</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124962302760363</v>
+        <v>1.124959171645605</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129747945780653</v>
+        <v>1.129741040439698</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136772158753857</v>
+        <v>1.136762336791793</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142656833905989</v>
+        <v>1.142640378184829</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14596433336228</v>
+        <v>1.145945105234989</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145781569843606</v>
+        <v>1.145758542647855</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.140017931203771</v>
+        <v>1.139993801018374</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138411171141235</v>
+        <v>1.138385774149655</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138261591522742</v>
+        <v>1.138234690659161</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.150000123707117</v>
+        <v>1.149982405276837</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165582755308856</v>
+        <v>1.165570936894372</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166046133301077</v>
+        <v>1.166035041517061</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180579658074264</v>
+        <v>1.180577808290791</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191652464929763</v>
+        <v>1.191661451450275</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199883645759371</v>
+        <v>1.199894480677175</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211680879545839</v>
+        <v>1.21169667271168</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205753969105298</v>
+        <v>1.205759130351754</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206591497779732</v>
+        <v>1.206600166363099</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210393813790303</v>
+        <v>1.210413237169262</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216233308729353</v>
+        <v>1.2162617206972</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222469681011627</v>
+        <v>1.222502476658085</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221045799079838</v>
+        <v>1.221071055726887</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208554865741735</v>
+        <v>1.208577580877867</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200247299919249</v>
+        <v>1.200268785017415</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189559282599812</v>
+        <v>1.189575557554188</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.18118596708451</v>
+        <v>1.181199667184017</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175927399504199</v>
+        <v>1.175937693648486</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172416885821405</v>
+        <v>1.172423791655156</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173758478156541</v>
+        <v>1.173770079288349</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.16975730724514</v>
+        <v>1.169764690113527</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168544867769064</v>
+        <v>1.168553486170589</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168678913191375</v>
+        <v>1.168692791357006</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166546637055793</v>
+        <v>1.166558596251554</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158283706295667</v>
+        <v>1.158292772449683</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151917309724499</v>
+        <v>1.151930313976509</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146357271197913</v>
+        <v>1.146370422854599</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143894403433061</v>
+        <v>1.143901772155675</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144544921434365</v>
+        <v>1.144542555426972</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146726589736214</v>
+        <v>1.146715448366527</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.14949616437969</v>
+        <v>1.149473031285259</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150898196381367</v>
+        <v>1.150866391654362</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150562581928539</v>
+        <v>1.150523171286848</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150087113289847</v>
+        <v>1.150040698541619</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148589163460801</v>
+        <v>1.148542199104435</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.146800695732576</v>
+        <v>1.146504657993474</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.145823201662862</v>
+        <v>1.145482627576209</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.144096707565605</v>
+        <v>1.143664701451912</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.143399333292739</v>
+        <v>1.142787825462965</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.145250561282714</v>
+        <v>1.144423702180189</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.146093369305293</v>
+        <v>1.145058485018919</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.147496286623899</v>
+        <v>1.146248918178614</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.149475255192349</v>
+        <v>1.147933626610524</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.151009429119355</v>
+        <v>1.149098718326135</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.144075024857068</v>
+        <v>1.141756150928995</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.139191352728517</v>
+        <v>1.136346565905404</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.116524128784161</v>
+        <v>1.113875543420279</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.07933515774562</v>
+        <v>1.078900425893751</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.083494028247831</v>
+        <v>1.079539121656974</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.146504657993474</v>
+        <v>1.146592055265095</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.145482627576209</v>
+        <v>1.145587346581423</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.143664701451912</v>
+        <v>1.143789175329631</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.142787825462965</v>
+        <v>1.142927869797865</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.144423702180189</v>
+        <v>1.144582656119704</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.145058485018919</v>
+        <v>1.145240089804958</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.146248918178614</v>
+        <v>1.146454960155226</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.147933626610524</v>
+        <v>1.148174191397422</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.149098718326135</v>
+        <v>1.149382221981223</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.141756150928995</v>
+        <v>1.142113069249387</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.136346565905404</v>
+        <v>1.136788204914438</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.113875543420279</v>
+        <v>1.114490963448725</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.078900425893751</v>
+        <v>1.079880600619695</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.079539121656974</v>
+        <v>1.081688961899105</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187206947850786</v>
+        <v>1.187208488710742</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178917897003089</v>
+        <v>1.178920341768842</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177419098350066</v>
+        <v>1.177421233286048</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172976612149266</v>
+        <v>1.172979618251916</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171750901973831</v>
+        <v>1.171754049357899</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169733107304978</v>
+        <v>1.169736356646482</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167265711242061</v>
+        <v>1.167268988016535</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165524616708472</v>
+        <v>1.165527875672156</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166516867986789</v>
+        <v>1.166519104302287</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161089737365738</v>
+        <v>1.161089419237631</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161572543264938</v>
+        <v>1.161572343440612</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160923212290043</v>
+        <v>1.160923059005297</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162113962470726</v>
+        <v>1.162112791573818</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159738563897231</v>
+        <v>1.15973798933289</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416440410191</v>
+        <v>1.155416484175668</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148472493789484</v>
+        <v>1.148472883294729</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140653381375</v>
+        <v>1.143140606204592</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137871822022971</v>
+        <v>1.13787093666522</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130120248590511</v>
+        <v>1.130117823303963</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124959171645605</v>
+        <v>1.124956099193912</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129741040439698</v>
+        <v>1.129734262660728</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136762336791793</v>
+        <v>1.136752695350511</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142640378184829</v>
+        <v>1.142624219908254</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145945105234989</v>
+        <v>1.145926223617137</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145758542647855</v>
+        <v>1.145735929514813</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139993801018374</v>
+        <v>1.139970102367458</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138385774149655</v>
+        <v>1.138360829077082</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138234690659161</v>
+        <v>1.138208265545506</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149982405276837</v>
+        <v>1.149964997816323</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165570936894372</v>
+        <v>1.165559326342217</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166035041517061</v>
+        <v>1.16602414318622</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180577808290791</v>
+        <v>1.180575989352456</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191661451450275</v>
+        <v>1.191670280646883</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199894480677175</v>
+        <v>1.19990512521576</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.21169667271168</v>
+        <v>1.211712183535762</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205759130351754</v>
+        <v>1.20576418813848</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206600166363099</v>
+        <v>1.206608666458459</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210413237169262</v>
+        <v>1.21043230161953</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.2162617206972</v>
+        <v>1.216289618648928</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222502476658085</v>
+        <v>1.222534680553702</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221071055726887</v>
+        <v>1.221095851658335</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208577580877867</v>
+        <v>1.208599884583748</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200268785017415</v>
+        <v>1.200289883164253</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189575557554188</v>
+        <v>1.189591543644887</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181199667184017</v>
+        <v>1.181213125351408</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175937693648486</v>
+        <v>1.17594780683411</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172423791655156</v>
+        <v>1.172430575804237</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173770079288349</v>
+        <v>1.17378147453456</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169764690113527</v>
+        <v>1.169771938674715</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168553486170589</v>
+        <v>1.168561947540908</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168692791357006</v>
+        <v>1.168706420499997</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166558596251554</v>
+        <v>1.16657034000574</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158292772449683</v>
+        <v>1.158301671161367</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151930313976509</v>
+        <v>1.151943088777871</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146370422854599</v>
+        <v>1.146383349601054</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143901772155675</v>
+        <v>1.143909027361431</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144542555426972</v>
+        <v>1.144540256063547</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146715448366527</v>
+        <v>1.14670452356639</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149473031285259</v>
+        <v>1.149450320592169</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150866391654362</v>
+        <v>1.150835138315407</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150523171286848</v>
+        <v>1.150484412980153</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.150040698541619</v>
+        <v>1.149995022817705</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148542199104435</v>
+        <v>1.148495929211904</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.146592055265095</v>
+        <v>1.146393000053993</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.145587346581423</v>
+        <v>1.145362216381026</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.143789175329631</v>
+        <v>1.143495288428618</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.142927869797865</v>
+        <v>1.142477004936828</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.144582656119704</v>
+        <v>1.14394498936452</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.145240089804958</v>
+        <v>1.144427883441289</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.146454960155226</v>
+        <v>1.145466436746209</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.148174191397422</v>
+        <v>1.146945703986836</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.149382221981223</v>
+        <v>1.147857371278196</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.142113069249387</v>
+        <v>1.140295905172706</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.136788204914438</v>
+        <v>1.134602997767781</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.114490963448725</v>
+        <v>1.112717007997484</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.079880600619695</v>
+        <v>1.080316175380122</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.081688961899105</v>
+        <v>1.080606834757373</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187208488710742</v>
+        <v>1.18721000180973</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178920341768842</v>
+        <v>1.178922742589426</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177421233286048</v>
+        <v>1.177423330110624</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172979618251916</v>
+        <v>1.172982570569787</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171754049357899</v>
+        <v>1.171757140399651</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169736356646482</v>
+        <v>1.169739547792982</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167268988016535</v>
+        <v>1.167272206091405</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165527875672156</v>
+        <v>1.165531076254022</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166519104302287</v>
+        <v>1.166521301143368</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161089419237631</v>
+        <v>1.161089107017411</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161572343440612</v>
+        <v>1.161572147384275</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160923059005297</v>
+        <v>1.160922908645619</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162112791573818</v>
+        <v>1.162111642093619</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15973798933289</v>
+        <v>1.159737425241304</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416484175668</v>
+        <v>1.155416527396383</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148472883294729</v>
+        <v>1.148473266753524</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140606204592</v>
+        <v>1.14314056150184</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.13787093666522</v>
+        <v>1.137870069720061</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130117823303963</v>
+        <v>1.130115443706675</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124956099193912</v>
+        <v>1.124953083774259</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129734262660728</v>
+        <v>1.1297276089449</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136752695350511</v>
+        <v>1.136743229503428</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142624219908254</v>
+        <v>1.142608351089292</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145926223617137</v>
+        <v>1.145907679234101</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145735929514813</v>
+        <v>1.145713719387626</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139970102367458</v>
+        <v>1.139946823792964</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138360829077082</v>
+        <v>1.138336323987146</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138208265545506</v>
+        <v>1.138182303697013</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149964997816323</v>
+        <v>1.149947893224611</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165559326342217</v>
+        <v>1.165547918223521</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.16602414318622</v>
+        <v>1.166013433300824</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180575989352456</v>
+        <v>1.180574200495578</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191670280646883</v>
+        <v>1.191678956608087</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.19990512521576</v>
+        <v>1.199915584341668</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211712183535762</v>
+        <v>1.211727419516816</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.20576418813848</v>
+        <v>1.205769145514363</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206608666458459</v>
+        <v>1.206617002902084</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.21043230161953</v>
+        <v>1.210451016983362</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216289618648928</v>
+        <v>1.216317016396567</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222534680553702</v>
+        <v>1.222566308553464</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221095851658335</v>
+        <v>1.221120199351542</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208599884583748</v>
+        <v>1.208621787921903</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200289883164253</v>
+        <v>1.200310604703022</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189591543644887</v>
+        <v>1.18960724847961</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181213125351408</v>
+        <v>1.181226347926319</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.17594780683411</v>
+        <v>1.17595774378441</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172430575804237</v>
+        <v>1.172437241452388</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.17378147453456</v>
+        <v>1.173792669320197</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169771938674715</v>
+        <v>1.169779056554311</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168561947540908</v>
+        <v>1.168570256125573</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168706420499997</v>
+        <v>1.168719807255077</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.16657034000574</v>
+        <v>1.16658187408294</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158301671161367</v>
+        <v>1.158310407017087</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151943088777871</v>
+        <v>1.151955640123855</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146383349601054</v>
+        <v>1.146396057118361</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143909027361431</v>
+        <v>1.143916171569479</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144540256063547</v>
+        <v>1.144538020955975</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.14670452356639</v>
+        <v>1.146693809211977</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149450320592169</v>
+        <v>1.149428021004245</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150835138315407</v>
+        <v>1.150804422395523</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150484412980153</v>
+        <v>1.15044629135422</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149995022817705</v>
+        <v>1.149950069248067</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148495929211904</v>
+        <v>1.148450339502368</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.146393000053993</v>
+        <v>1.146140519245326</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.145362216381026</v>
+        <v>1.145041631070458</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.143495288428618</v>
+        <v>1.143086468155386</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.142477004936828</v>
+        <v>1.141911866955891</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.14394498936452</v>
+        <v>1.143188106578116</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.144427883441289</v>
+        <v>1.143488739563444</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.145466436746209</v>
+        <v>1.144342390739374</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.146945703986836</v>
+        <v>1.145569359650683</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.147857371278196</v>
+        <v>1.14617025954763</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.140295905172706</v>
+        <v>1.138270360844524</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.134602997767781</v>
+        <v>1.132177901603623</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.112717007997484</v>
+        <v>1.110548348993297</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.080316175380122</v>
+        <v>1.07972620518368</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.080606834757373</v>
+        <v>1.078117988328941</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B122"/>
+  <dimension ref="A1:B123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.18721000180973</v>
+        <v>1.187211487891267</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178922742589426</v>
+        <v>1.178925100639104</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177423330110624</v>
+        <v>1.177425389835102</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172982570569787</v>
+        <v>1.172985470533341</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171757140399651</v>
+        <v>1.171760176598362</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169739547792982</v>
+        <v>1.169742682293783</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167272206091405</v>
+        <v>1.167275367029764</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165531076254022</v>
+        <v>1.165534220008734</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166521301143368</v>
+        <v>1.166523459545461</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161089107017411</v>
+        <v>1.161088800542163</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161572147384275</v>
+        <v>1.161571954990543</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160922908645619</v>
+        <v>1.160922761128319</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162111642093619</v>
+        <v>1.162110513448086</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159737425241304</v>
+        <v>1.159736871338879</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416527396383</v>
+        <v>1.15541657008036</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148473266753524</v>
+        <v>1.148473644301899</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14314056150184</v>
+        <v>1.143140519163814</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137870069720061</v>
+        <v>1.137869220629448</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130115443706675</v>
+        <v>1.13011310852269</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124953083774259</v>
+        <v>1.124950123815452</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.1297276089449</v>
+        <v>1.129721075920048</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136743229503428</v>
+        <v>1.136733934501442</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142608351089292</v>
+        <v>1.142592764024193</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145907679234101</v>
+        <v>1.145889463139024</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145713719387626</v>
+        <v>1.14569190159922</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139946823792964</v>
+        <v>1.139923954238373</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138336323987146</v>
+        <v>1.138312247359475</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138182303697013</v>
+        <v>1.138156793061065</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149947893224611</v>
+        <v>1.149931083679183</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165547918223521</v>
+        <v>1.165536707296581</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166013433300824</v>
+        <v>1.166002907024161</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180574200495578</v>
+        <v>1.180572440981433</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191678956608087</v>
+        <v>1.191687483282183</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199915584341668</v>
+        <v>1.199925862850439</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211727419516816</v>
+        <v>1.211742387890554</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205769145514363</v>
+        <v>1.205774005410647</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206617002902084</v>
+        <v>1.206625180347843</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210451016983362</v>
+        <v>1.210469392746973</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216317016396567</v>
+        <v>1.216343927262105</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222566308553464</v>
+        <v>1.222597375951588</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221120199351542</v>
+        <v>1.221144110837857</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208621787921903</v>
+        <v>1.208643301562319</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200310604703022</v>
+        <v>1.200330959612204</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.18960724847961</v>
+        <v>1.189622679401776</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181226347926319</v>
+        <v>1.181239341029257</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.17595774378441</v>
+        <v>1.175967509059991</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172437241452388</v>
+        <v>1.172443791673399</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173792669320197</v>
+        <v>1.173803668881614</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169779056554311</v>
+        <v>1.16978604724881</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168570256125573</v>
+        <v>1.168578416018717</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168719807255077</v>
+        <v>1.168732958023642</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.16658187408294</v>
+        <v>1.166593204044079</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158310407017087</v>
+        <v>1.158318984437567</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151955640123855</v>
+        <v>1.151967973803543</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146396057118361</v>
+        <v>1.146408550899285</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143916171569479</v>
+        <v>1.143923207228326</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144538020955975</v>
+        <v>1.144535847820436</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146693809211977</v>
+        <v>1.146683299404067</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149428021004245</v>
+        <v>1.149406121618864</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150804422395523</v>
+        <v>1.150774230384928</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.15044629135422</v>
+        <v>1.150408791236801</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149950069248067</v>
+        <v>1.149905821448383</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148450339502368</v>
+        <v>1.148405416043613</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.146140519245326</v>
+        <v>1.146107406334093</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.145041631070458</v>
+        <v>1.144773475713432</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.143086468155386</v>
+        <v>1.142814112898821</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.141911866955891</v>
+        <v>1.141641879458622</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.143188106578116</v>
+        <v>1.142767812346856</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.143488739563444</v>
+        <v>1.142961910935573</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.144342390739374</v>
+        <v>1.143748165215048</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.145569359650683</v>
+        <v>1.144889769009683</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.14617025954763</v>
+        <v>1.145388314990174</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.138270360844524</v>
+        <v>1.137653727061105</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.132177901603623</v>
+        <v>1.131619467587677</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.110548348993297</v>
+        <v>1.111006381911729</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.07972620518368</v>
+        <v>1.08282142014911</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,15 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.078117988328941</v>
+        <v>1.082526343830679</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B123">
+        <v>1.098066343830679</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187211487891267</v>
+        <v>1.187212947672554</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178925100639104</v>
+        <v>1.178927417050671</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177425389835102</v>
+        <v>1.177427413435329</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172985470533341</v>
+        <v>1.172988319522766</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171760176598362</v>
+        <v>1.171763159400582</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169742682293783</v>
+        <v>1.169745761643684</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167275367029764</v>
+        <v>1.167278472339699</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165534220008734</v>
+        <v>1.16553730843625</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166523459545461</v>
+        <v>1.166525580508118</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161088800542163</v>
+        <v>1.161088499654904</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161571954990543</v>
+        <v>1.161571766157921</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160922761128319</v>
+        <v>1.160922616373781</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162110513448086</v>
+        <v>1.162109405076071</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159736871338879</v>
+        <v>1.159736327352164</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541657008036</v>
+        <v>1.155416612235567</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148473644301899</v>
+        <v>1.148474016071981</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140519163814</v>
+        <v>1.143140479086583</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137869220629448</v>
+        <v>1.137868388857345</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.13011310852269</v>
+        <v>1.130110816523019</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124950123815452</v>
+        <v>1.124947217803413</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129721075920048</v>
+        <v>1.129714660335006</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136733934501442</v>
+        <v>1.136724805765022</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142592764024193</v>
+        <v>1.14257745128</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145889463139024</v>
+        <v>1.14587156669848</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.14569190159922</v>
+        <v>1.145670465855299</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139923954238373</v>
+        <v>1.139901483031291</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138312247359475</v>
+        <v>1.138288588071762</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138156793061065</v>
+        <v>1.138131721998697</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149931083679183</v>
+        <v>1.149914561624128</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165536707296581</v>
+        <v>1.165525688498877</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166002907024161</v>
+        <v>1.165992559683318</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180572440981433</v>
+        <v>1.18057071009525</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191687483282183</v>
+        <v>1.191695864483212</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199925862850439</v>
+        <v>1.199935965373899</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211742387890554</v>
+        <v>1.211757095641084</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205774005410647</v>
+        <v>1.205778770646506</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206625180347843</v>
+        <v>1.206633203275685</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210469392746973</v>
+        <v>1.210487438056461</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216343927262105</v>
+        <v>1.216370364099016</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222597375951588</v>
+        <v>1.222627897506067</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221144110837857</v>
+        <v>1.221167597722351</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208643301562319</v>
+        <v>1.208664435799677</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200330959612204</v>
+        <v>1.200350957521416</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189622679401776</v>
+        <v>1.189637843501874</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181239341029257</v>
+        <v>1.181252110570965</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175967509059991</v>
+        <v>1.175977107065668</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172443791673399</v>
+        <v>1.17245022943581</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173803668881614</v>
+        <v>1.17381447827461</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.16978604724881</v>
+        <v>1.169792914131277</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168578416018717</v>
+        <v>1.168586431169733</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168732958023642</v>
+        <v>1.168745878983913</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166593204044079</v>
+        <v>1.166604335255333</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158318984437567</v>
+        <v>1.158327407685289</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151967973803543</v>
+        <v>1.151980095408573</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146408550899285</v>
+        <v>1.146420836255953</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143923207228326</v>
+        <v>1.143930136718122</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144535847820436</v>
+        <v>1.144533734472038</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146683299404067</v>
+        <v>1.146672988458008</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149406121618864</v>
+        <v>1.149384611910206</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150774230384928</v>
+        <v>1.150744549214709</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150408791236801</v>
+        <v>1.150371897919918</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149905821448383</v>
+        <v>1.149862263503834</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148405416043613</v>
+        <v>1.148361145243605</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.146107406334093</v>
+        <v>1.146074696037899</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.144773475713432</v>
+        <v>1.144510724766592</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.142814112898821</v>
+        <v>1.142547078399267</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.141641879458622</v>
+        <v>1.141374860880563</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.142767812346856</v>
+        <v>1.142355386052267</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.142961910935573</v>
+        <v>1.142443368033581</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.143748165215048</v>
+        <v>1.143163458668296</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.144889769009683</v>
+        <v>1.144222435606792</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.145388314990174</v>
+        <v>1.144623147230916</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.137653727061105</v>
+        <v>1.137042795727425</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.131619467587677</v>
+        <v>1.131057465843723</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.111006381911729</v>
+        <v>1.111348260614953</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.08282142014911</v>
+        <v>1.085337986713991</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.082526343830679</v>
+        <v>1.085672942535129</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.098066343830679</v>
+        <v>1.09978008072476</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.144510724766592</v>
+        <v>1.144395657144345</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.142547078399267</v>
+        <v>1.142412153341689</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.141374860880563</v>
+        <v>1.141230880383199</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.142355386052267</v>
+        <v>1.14222875625158</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.142443368033581</v>
+        <v>1.14227056705405</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.143163458668296</v>
+        <v>1.142953568668956</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.144222435606792</v>
+        <v>1.143962759727282</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.144623147230916</v>
+        <v>1.144303275735691</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.137042795727425</v>
+        <v>1.13664409594503</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.131057465843723</v>
+        <v>1.130515763031394</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.111348260614953</v>
+        <v>1.110593632415495</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.085337986713991</v>
+        <v>1.084215020178476</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.085672942535129</v>
+        <v>1.083803957728165</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.09978008072476</v>
+        <v>1.092214104878717</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187212947672554</v>
+        <v>1.187214381845632</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178927417050671</v>
+        <v>1.178929692917275</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177427413435329</v>
+        <v>1.177429401853231</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172988319522766</v>
+        <v>1.172991118870165</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171763159400582</v>
+        <v>1.171766090202442</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169745761643684</v>
+        <v>1.169748787285354</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167278472339699</v>
+        <v>1.167281523476696</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.16553730843625</v>
+        <v>1.165540342984204</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166525580508118</v>
+        <v>1.166527664996555</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161088499654904</v>
+        <v>1.161088204204312</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161571766157921</v>
+        <v>1.161571580788622</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160922616373781</v>
+        <v>1.160922474305333</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162109405076071</v>
+        <v>1.162108316436391</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159736327352164</v>
+        <v>1.159735793017401</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416612235567</v>
+        <v>1.15541665386992</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148474016071981</v>
+        <v>1.148474382192126</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140479086583</v>
+        <v>1.14314044117129</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137868388857345</v>
+        <v>1.137867573888667</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130110816523019</v>
+        <v>1.130108566523507</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124947217803413</v>
+        <v>1.124944364278611</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129714660335006</v>
+        <v>1.129708359054241</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136724805765022</v>
+        <v>1.136715838876715</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14257745128</v>
+        <v>1.142562405682758</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.14587156669848</v>
+        <v>1.145853981578876</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145670465855299</v>
+        <v>1.145649402218214</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139901483031291</v>
+        <v>1.139879399866936</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138288588071762</v>
+        <v>1.138265335382742</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138131721998697</v>
+        <v>1.138107079267037</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149914561624128</v>
+        <v>1.149898319758895</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165525688498877</v>
+        <v>1.165514856939492</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.165992559683318</v>
+        <v>1.165982386762319</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.18057071009525</v>
+        <v>1.180569007145244</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191695864483212</v>
+        <v>1.191704103896605</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199935965373899</v>
+        <v>1.199945896387072</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211757095641084</v>
+        <v>1.211771549511749</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205778770646506</v>
+        <v>1.205783443934319</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206633203275685</v>
+        <v>1.206641075999651</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210487438056461</v>
+        <v>1.210505161732895</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216370364099016</v>
+        <v>1.216396339312654</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222627897506067</v>
+        <v>1.222657887461944</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221167597722351</v>
+        <v>1.221190671202506</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208664435799677</v>
+        <v>1.208685200569686</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200350957521416</v>
+        <v>1.200370607726499</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189637843501874</v>
+        <v>1.189652747628241</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181252110570965</v>
+        <v>1.181264662261313</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175977107065668</v>
+        <v>1.175986542057045</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.17245022943581</v>
+        <v>1.172456557607374</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.17381447827461</v>
+        <v>1.173825102382142</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169792914131277</v>
+        <v>1.169799660456743</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168586431169733</v>
+        <v>1.168594305389605</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168745878983913</v>
+        <v>1.168758576100567</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166604335255333</v>
+        <v>1.166615272896566</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158327407685289</v>
+        <v>1.158335680871494</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151980095408573</v>
+        <v>1.151992010341455</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146420836255953</v>
+        <v>1.146432918327152</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143930136718122</v>
+        <v>1.143936962352874</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144533734472038</v>
+        <v>1.144531678819769</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146672988458008</v>
+        <v>1.146662870894205</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149384611910206</v>
+        <v>1.149363481713335</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150744549214709</v>
+        <v>1.15071536623934</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150371897919918</v>
+        <v>1.150335597142879</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149862263503834</v>
+        <v>1.149819379953458</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148361145243605</v>
+        <v>1.148317513842128</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.146074696037899</v>
+        <v>1.14604238245817</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.144395657144345</v>
+        <v>1.143843585098481</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.142412153341689</v>
+        <v>1.141788549758383</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.141230880383199</v>
+        <v>1.140555592681224</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.14222875625158</v>
+        <v>1.141355059754288</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.14227056705405</v>
+        <v>1.141224638555182</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.142953568668956</v>
+        <v>1.141776991500196</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.143962759727282</v>
+        <v>1.142598590827178</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.144303275735691</v>
+        <v>1.142718952048043</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.13664409594503</v>
+        <v>1.135026638231135</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.130515763031394</v>
+        <v>1.128609285795086</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.110593632415495</v>
+        <v>1.109021565837702</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.084215020178476</v>
+        <v>1.083688155929819</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.083803957728165</v>
+        <v>1.082080744468533</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.092214104878717</v>
+        <v>1.081301021445213</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187214381845632</v>
+        <v>1.187215791078471</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178929692917275</v>
+        <v>1.178931929294131</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177429401853231</v>
+        <v>1.177431355998277</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172991118870165</v>
+        <v>1.172993869861634</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171766090202442</v>
+        <v>1.171768970351826</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169748787285354</v>
+        <v>1.169751760611588</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167281523476696</v>
+        <v>1.167284521845909</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165540342984204</v>
+        <v>1.165543325050171</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166527664996555</v>
+        <v>1.16652971394311</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161088204204312</v>
+        <v>1.161087914044479</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161571580788622</v>
+        <v>1.161571398788402</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160922474305333</v>
+        <v>1.160922334849102</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162108316436391</v>
+        <v>1.162107247006948</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159735793017401</v>
+        <v>1.159735268080099</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541665386992</v>
+        <v>1.155416694991266</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148474382192126</v>
+        <v>1.148474742787048</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14314044117129</v>
+        <v>1.143140405323872</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137867573888667</v>
+        <v>1.137866775228273</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130108566523507</v>
+        <v>1.130106357382811</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124944364278611</v>
+        <v>1.124941561833626</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129708359054241</v>
+        <v>1.129702169052753</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136715838876715</v>
+        <v>1.136707029574038</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142562405682758</v>
+        <v>1.142547620306341</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145853981578876</v>
+        <v>1.145836699733562</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145649402218214</v>
+        <v>1.145628701091671</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139879399866936</v>
+        <v>1.139857694792465</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138265335382742</v>
+        <v>1.138242478916047</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138107079267037</v>
+        <v>1.138082854002637</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149898319758895</v>
+        <v>1.149882351027623</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165514856939492</v>
+        <v>1.165504207891909</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.165982386762319</v>
+        <v>1.165972383895598</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180569007145244</v>
+        <v>1.180567331461709</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191704103896605</v>
+        <v>1.191712205084553</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199945896387072</v>
+        <v>1.199955660214754</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211771549511749</v>
+        <v>1.211785756015403</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205783443934319</v>
+        <v>1.20578802788464</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206641075999651</v>
+        <v>1.206648802675452</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210505161732895</v>
+        <v>1.210522572286609</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216396339312654</v>
+        <v>1.216421864879601</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222657887461944</v>
+        <v>1.222687359573379</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221190671202506</v>
+        <v>1.221213342085941</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208685200569686</v>
+        <v>1.20870560546458</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200370607726499</v>
+        <v>1.200389919203833</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189652747628241</v>
+        <v>1.189667398397284</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181264662261313</v>
+        <v>1.181277001617744</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175986542057045</v>
+        <v>1.175995818146778</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172456557607374</v>
+        <v>1.172462778959286</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173825102382142</v>
+        <v>1.173835545921631</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169799660456743</v>
+        <v>1.16980628936731</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168594305389605</v>
+        <v>1.168602042356905</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168758576100567</v>
+        <v>1.168771055133871</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166615272896566</v>
+        <v>1.166626021969348</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158335680871494</v>
+        <v>1.158343807962819</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151992010341455</v>
+        <v>1.15200372382346</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146432918327152</v>
+        <v>1.146444802085296</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143936962352874</v>
+        <v>1.14394368638258</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144531678819769</v>
+        <v>1.144529678861746</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146662870894205</v>
+        <v>1.146652941429102</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149363481713335</v>
+        <v>1.14934272120908</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.15071536623934</v>
+        <v>1.150686669220016</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150335597142879</v>
+        <v>1.150299875076001</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149819379953458</v>
+        <v>1.14977715577507</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148317513842128</v>
+        <v>1.148274508902537</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.14604238245817</v>
+        <v>1.146010459747395</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.143843585098481</v>
+        <v>1.143313935207247</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.141788549758383</v>
+        <v>1.141190477663629</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.140555592681224</v>
+        <v>1.139911782873189</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.141355059754288</v>
+        <v>1.140523385475261</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.141224638555182</v>
+        <v>1.140227073668398</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.141776991500196</v>
+        <v>1.140655316098116</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.142598590827178</v>
+        <v>1.141301894452772</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.142718952048043</v>
+        <v>1.141220199886571</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.135026638231135</v>
+        <v>1.133507720594808</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.128609285795086</v>
+        <v>1.126839744980041</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.109021565837702</v>
+        <v>1.107593768127378</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.083688155929819</v>
+        <v>1.083217796010538</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.082080744468533</v>
+        <v>1.080682362363043</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.081301021445213</v>
+        <v>1.075794902822316</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187215791078471</v>
+        <v>1.187217176016013</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178931929294131</v>
+        <v>1.178934127200153</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177431355998277</v>
+        <v>1.177433276748858</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172993869861634</v>
+        <v>1.172996573739229</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171768970351826</v>
+        <v>1.171771801150439</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169751760611588</v>
+        <v>1.169754682967441</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167284521845909</v>
+        <v>1.16728746880432</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165543325050171</v>
+        <v>1.165546255983813</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.16652971394311</v>
+        <v>1.166531728248628</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161087914044479</v>
+        <v>1.161087629034665</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161571398788402</v>
+        <v>1.161571220066397</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160922334849102</v>
+        <v>1.160922197933895</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162107247006948</v>
+        <v>1.162106196283895</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159735268080099</v>
+        <v>1.159734752294632</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416694991266</v>
+        <v>1.15541673560738</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148474742787048</v>
+        <v>1.14847509797794</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140405323872</v>
+        <v>1.143140371454793</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137866775228273</v>
+        <v>1.137865992400025</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130106357382811</v>
+        <v>1.130104188000485</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124941561833626</v>
+        <v>1.124938809110856</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129702169052753</v>
+        <v>1.129696087411259</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136707029574038</v>
+        <v>1.136698373742756</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142547620306341</v>
+        <v>1.142533088461844</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145836699733562</v>
+        <v>1.145819713390596</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145628701091671</v>
+        <v>1.14560835320621</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139857694792465</v>
+        <v>1.139836358192094</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138242478916047</v>
+        <v>1.138220008644859</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138082854002637</v>
+        <v>1.138059035705625</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149882351027623</v>
+        <v>1.149866648608991</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165504207891909</v>
+        <v>1.165493736787171</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.165972383895598</v>
+        <v>1.165962546861812</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180567331461709</v>
+        <v>1.180565682396135</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191712205084553</v>
+        <v>1.191720171491106</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199955660214754</v>
+        <v>1.199965261037752</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211785756015403</v>
+        <v>1.211799721444173</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.20578802788464</v>
+        <v>1.205792525010904</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206648802675452</v>
+        <v>1.206656387307634</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210522572286609</v>
+        <v>1.210539677930743</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216421864879601</v>
+        <v>1.216446952366018</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222687359573379</v>
+        <v>1.222716327124592</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221213342085941</v>
+        <v>1.221235620807203</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20870560546458</v>
+        <v>1.208725659747809</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200389919203833</v>
+        <v>1.200408900623925</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189667398397284</v>
+        <v>1.189681802203204</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181277001617744</v>
+        <v>1.181289133973294</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175995818146778</v>
+        <v>1.176004939310515</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172462778959286</v>
+        <v>1.172468896170213</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173835545921631</v>
+        <v>1.173845813451913</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.16980628936731</v>
+        <v>1.169812803897</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168602042356905</v>
+        <v>1.168609645623492</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168771055133871</v>
+        <v>1.168783321648355</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166626021969348</v>
+        <v>1.166636587304545</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158343807962819</v>
+        <v>1.158351792787585</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.15200372382346</v>
+        <v>1.152015240902133</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146444802085296</v>
+        <v>1.146456492343047</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14394368638258</v>
+        <v>1.143950310995291</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144529678861746</v>
+        <v>1.144527732680737</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146652941429102</v>
+        <v>1.146643194966624</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.14934272120908</v>
+        <v>1.149322320909648</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150686669220016</v>
+        <v>1.150658446308739</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150299875076001</v>
+        <v>1.150264718304996</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.14977715577507</v>
+        <v>1.149735576370723</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148274508902537</v>
+        <v>1.148232117803644</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.146010459747395</v>
+        <v>1.145978922112992</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.143313935207247</v>
+        <v>1.142859716164049</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.141190477663629</v>
+        <v>1.140685372812334</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.139911782873189</v>
+        <v>1.13937390679682</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.140523385475261</v>
+        <v>1.139830239965229</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.140227073668398</v>
+        <v>1.139381926348338</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.140655316098116</v>
+        <v>1.139702841095772</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.141301894452772</v>
+        <v>1.14020354293674</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.141220199886571</v>
+        <v>1.139957554483412</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.133507720594808</v>
+        <v>1.132265720052837</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.126839744980041</v>
+        <v>1.12543857114949</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.107593768127378</v>
+        <v>1.106615140418872</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.083217796010538</v>
+        <v>1.08324182742012</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.080682362363043</v>
+        <v>1.080184652865627</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.075794902822316</v>
+        <v>1.073930378026248</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187217176016013</v>
+        <v>1.187218537281155</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178934127200153</v>
+        <v>1.178936287619504</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177433276748858</v>
+        <v>1.17743516495361</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172996573739229</v>
+        <v>1.172999231702834</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171771801150439</v>
+        <v>1.171774583855771</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169754682967441</v>
+        <v>1.169757555652255</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.16728746880432</v>
+        <v>1.167290365662784</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165546255983813</v>
+        <v>1.165549137088909</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166531728248628</v>
+        <v>1.166533708783787</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161087629034665</v>
+        <v>1.161087349039076</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161571220066397</v>
+        <v>1.161571044534982</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160922197933895</v>
+        <v>1.160922063491077</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162106196283895</v>
+        <v>1.162105163780846</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159734752294632</v>
+        <v>1.159734245423856</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541673560738</v>
+        <v>1.155416775725963</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.14847509797794</v>
+        <v>1.148475447882589</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140371454793</v>
+        <v>1.1431403394788</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137865992400025</v>
+        <v>1.137865224945893</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130104188000485</v>
+        <v>1.130102057315169</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124938809110856</v>
+        <v>1.124936104800325</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129696087411259</v>
+        <v>1.12969011131161</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136698373742756</v>
+        <v>1.136689867410489</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142533088461844</v>
+        <v>1.142518803687524</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145819713390596</v>
+        <v>1.145803015041128</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.14560835320621</v>
+        <v>1.145588349605425</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139836358192094</v>
+        <v>1.13981538077297</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138220008644859</v>
+        <v>1.138197914877341</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138059035705625</v>
+        <v>1.138035614224661</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149866648608991</v>
+        <v>1.149851205906566</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165493736787171</v>
+        <v>1.165483439207381</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.165962546861812</v>
+        <v>1.165952871577935</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180565682396135</v>
+        <v>1.180564059320386</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191720171491106</v>
+        <v>1.191728006447019</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199965261037752</v>
+        <v>1.199974702898821</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211799721444173</v>
+        <v>1.21181345187872</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205792525010904</v>
+        <v>1.20579693773387</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206656387307634</v>
+        <v>1.206663833756363</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210539677930743</v>
+        <v>1.210556486594089</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216446952366018</v>
+        <v>1.216471612945061</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222716327124592</v>
+        <v>1.222744802949744</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221235620807203</v>
+        <v>1.221257517443721</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208725659747809</v>
+        <v>1.20874537236799</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200408900623925</v>
+        <v>1.200427560364301</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189681802203204</v>
+        <v>1.189695965227224</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181289133973294</v>
+        <v>1.181301064484221</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.176004939310515</v>
+        <v>1.176013909392547</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172468896170213</v>
+        <v>1.172474911830115</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173845813451913</v>
+        <v>1.173855909379836</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169812803897</v>
+        <v>1.169819206976359</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168609645623492</v>
+        <v>1.168617118619907</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168783321648355</v>
+        <v>1.168795381021044</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166636587304545</v>
+        <v>1.166646973569541</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158351792787585</v>
+        <v>1.158359639041767</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.152015240902133</v>
+        <v>1.152026566458423</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146456492343047</v>
+        <v>1.146467993759633</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143950310995291</v>
+        <v>1.143956838319102</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144527732680737</v>
+        <v>1.144525838439943</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146643194966624</v>
+        <v>1.146633626590063</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149322320909648</v>
+        <v>1.149302271644945</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150658446308739</v>
+        <v>1.150630686033138</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150264718304996</v>
+        <v>1.15023011381602</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149735576370723</v>
+        <v>1.149694627552692</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148232117803644</v>
+        <v>1.148190328231715</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.145978922112992</v>
+        <v>1.145947763820703</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.142859716164049</v>
+        <v>1.14242348143458</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.140685372812334</v>
+        <v>1.140199392588645</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.13937390679682</v>
+        <v>1.138854933215538</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.139830239965229</v>
+        <v>1.139164154430389</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.139381926348338</v>
+        <v>1.138568897618094</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.139702841095772</v>
+        <v>1.138787028199405</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.14020354293674</v>
+        <v>1.13914997197111</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.139957554483412</v>
+        <v>1.138750981060767</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.132265720052837</v>
+        <v>1.131084199370866</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.12543857114949</v>
+        <v>1.124116817568225</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.106615140418872</v>
+        <v>1.105698192240629</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.08324182742012</v>
+        <v>1.083226974969588</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.080184652865627</v>
+        <v>1.079721515307657</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.073930378026248</v>
+        <v>1.072596331744058</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B123"/>
+  <dimension ref="A1:B124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187218537281155</v>
+        <v>1.187219875475677</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178936287619504</v>
+        <v>1.178938411503063</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.17743516495361</v>
+        <v>1.177437021432659</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172999231702834</v>
+        <v>1.173001844911938</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171774583855771</v>
+        <v>1.171777319682951</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169757555652255</v>
+        <v>1.169760379921587</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167290365662784</v>
+        <v>1.167293213687967</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165549137088909</v>
+        <v>1.165551969625294</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166533708783787</v>
+        <v>1.16653565639034</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161087349039076</v>
+        <v>1.161087073926645</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161571044534982</v>
+        <v>1.161570872109616</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160922063491077</v>
+        <v>1.160921931454456</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162105163780846</v>
+        <v>1.162104149028126</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159734245423856</v>
+        <v>1.159733747238746</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416775725963</v>
+        <v>1.155416815354631</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148475447882589</v>
+        <v>1.148475792615493</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.1431403394788</v>
+        <v>1.143140309314686</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137865224945893</v>
+        <v>1.137864472425109</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130102057315169</v>
+        <v>1.130099964302871</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124936104800325</v>
+        <v>1.124933447637619</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.12969011131161</v>
+        <v>1.129684238032463</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136689867410489</v>
+        <v>1.136681506740664</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142518803687524</v>
+        <v>1.14250475973924</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145803015041128</v>
+        <v>1.145786597428373</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145588349605425</v>
+        <v>1.145568681632869</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.13981538077297</v>
+        <v>1.139794753551743</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138197914877341</v>
+        <v>1.138176188242783</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138035614224661</v>
+        <v>1.138012579742614</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149851205906566</v>
+        <v>1.149836016539631</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165483439207381</v>
+        <v>1.165473310879511</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.165952871577935</v>
+        <v>1.165943354093656</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180564059320386</v>
+        <v>1.180562461625902</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191728006447019</v>
+        <v>1.191735713174369</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199974702898821</v>
+        <v>1.199983989708305</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.21181345187872</v>
+        <v>1.211826953197046</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.20579693773387</v>
+        <v>1.205801268385825</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206663833756363</v>
+        <v>1.206671145743842</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210556486594089</v>
+        <v>1.210573005933271</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216471612945061</v>
+        <v>1.21649585741342</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222744802949744</v>
+        <v>1.222772799451816</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221257517443721</v>
+        <v>1.221279041730933</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20874537236799</v>
+        <v>1.208764751972155</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200427560364301</v>
+        <v>1.200445906521765</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189695965227224</v>
+        <v>1.189709893446371</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181301064484221</v>
+        <v>1.18131279813725</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.176013909392547</v>
+        <v>1.176022732111182</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172474911830115</v>
+        <v>1.172480828443887</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173855909379836</v>
+        <v>1.173865837966536</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169819206976359</v>
+        <v>1.169825501436818</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168617118619907</v>
+        <v>1.168624464660504</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168795381021044</v>
+        <v>1.168807238449287</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166646973569541</v>
+        <v>1.166657185275088</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158359639041767</v>
+        <v>1.158367350294653</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.152026566458423</v>
+        <v>1.152037705213479</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146467993759633</v>
+        <v>1.146479310846871</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143956838319102</v>
+        <v>1.143963270424075</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144525838439943</v>
+        <v>1.144523994379025</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146633626590063</v>
+        <v>1.146624231554377</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149302271644945</v>
+        <v>1.149282564549558</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150630686033138</v>
+        <v>1.150603377281973</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.15023011381602</v>
+        <v>1.150196048981315</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149694627552692</v>
+        <v>1.149654295529953</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148190328231715</v>
+        <v>1.148149128172622</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.145947763820703</v>
+        <v>1.145916979197563</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.14242348143458</v>
+        <v>1.142408596533985</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.140199392588645</v>
+        <v>1.139840568275651</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.138854933215538</v>
+        <v>1.138493603684488</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.139164154430389</v>
+        <v>1.138779731753804</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.138568897618094</v>
+        <v>1.138247774224615</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.138787028199405</v>
+        <v>1.138442698099247</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.13914997197111</v>
+        <v>1.138764886004072</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.138750981060767</v>
+        <v>1.138324933190548</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.131084199370866</v>
+        <v>1.130822284205211</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.124116817568225</v>
+        <v>1.124006706714185</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.105698192240629</v>
+        <v>1.105957244370314</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.083226974969588</v>
+        <v>1.084774713838653</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.079721515307657</v>
+        <v>1.081717339961145</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,15 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.072596331744058</v>
+        <v>1.076478343300753</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="3">
+        <v>46395</v>
+      </c>
+      <c r="B124">
+        <v>1.092018343300753</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.138493603684488</v>
+        <v>1.138494026315052</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.138779731753804</v>
+        <v>1.138773055098598</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.138247774224615</v>
+        <v>1.13817005156953</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.138442698099247</v>
+        <v>1.138384123701702</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.138764886004072</v>
+        <v>1.138712368192992</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.138324933190548</v>
+        <v>1.138274713810319</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.130822284205211</v>
+        <v>1.130771152408205</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.124006706714185</v>
+        <v>1.123951443717742</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.105957244370314</v>
+        <v>1.10594743842199</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.084774713838653</v>
+        <v>1.084765989132923</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.081717339961145</v>
+        <v>1.081709219504096</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.076478343300753</v>
+        <v>1.076468295649851</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>46395</v>
       </c>
       <c r="B124">
-        <v>1.092018343300753</v>
+        <v>1.092008295649851</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187219875475677</v>
+        <v>1.187221191181136</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178938411503063</v>
+        <v>1.178940499769819</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177437021432659</v>
+        <v>1.177438846978812</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.173001844911938</v>
+        <v>1.173004414487319</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171777319682951</v>
+        <v>1.17178000980652</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169760379921587</v>
+        <v>1.169763156989036</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167293213687967</v>
+        <v>1.167296014104204</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165551969625294</v>
+        <v>1.165554754810693</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.16653565639034</v>
+        <v>1.166537571882313</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161087073926645</v>
+        <v>1.161086803570832</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161570872109616</v>
+        <v>1.161570702708718</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160921931454456</v>
+        <v>1.160921801760176</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162104149028126</v>
+        <v>1.162103151572061</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159733747238746</v>
+        <v>1.159733257518053</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416815354631</v>
+        <v>1.155416854500915</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148475792615493</v>
+        <v>1.148476132287965</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140309314686</v>
+        <v>1.143140280885075</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137864472425109</v>
+        <v>1.137863734413374</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130099964302871</v>
+        <v>1.130097907975341</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124933447637619</v>
+        <v>1.124930836401927</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129684238032463</v>
+        <v>1.129678464945153</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136681506740664</v>
+        <v>1.136673288026759</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14250475973924</v>
+        <v>1.14249095058138</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145786597428373</v>
+        <v>1.145770453537127</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145568681632869</v>
+        <v>1.145549340919613</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139794753551743</v>
+        <v>1.139774467841804</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138176188242783</v>
+        <v>1.138154819678432</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138012579742614</v>
+        <v>1.137989922762951</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149836016539631</v>
+        <v>1.149821074334454</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165473310879511</v>
+        <v>1.165463347669526</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.165943354093656</v>
+        <v>1.165933990586035</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180562461625902</v>
+        <v>1.180560888722947</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191735713174369</v>
+        <v>1.191743294790944</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199983989708305</v>
+        <v>1.199993125249507</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211826953197046</v>
+        <v>1.211840231082863</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205801268385825</v>
+        <v>1.205805519214565</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206671145743842</v>
+        <v>1.2066783268604</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210573005933271</v>
+        <v>1.210589243344314</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.21649585741342</v>
+        <v>1.216519696207031</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222772799451816</v>
+        <v>1.222800328620548</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221279041730933</v>
+        <v>1.221300203076658</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208764751972155</v>
+        <v>1.208783806918331</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200445906521765</v>
+        <v>1.20046394692404</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189709893446371</v>
+        <v>1.189723592641815</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.18131279813725</v>
+        <v>1.181324339756476</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.176022732111182</v>
+        <v>1.176031411063858</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172480828443887</v>
+        <v>1.172486648434811</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173865837966536</v>
+        <v>1.173875603333399</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169825501436818</v>
+        <v>1.169831690014846</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168624464660504</v>
+        <v>1.168631686948319</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168807238449287</v>
+        <v>1.168818898958186</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166657185275088</v>
+        <v>1.166667226781816</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158367350294653</v>
+        <v>1.158374929994211</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.152037705213479</v>
+        <v>1.152048661735105</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146479310846871</v>
+        <v>1.146490447974909</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143963270424075</v>
+        <v>1.143969609324096</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144523994379025</v>
+        <v>1.144522198810352</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146624231554377</v>
+        <v>1.146615005278867</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149282564549558</v>
+        <v>1.149263191050367</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150603377281973</v>
+        <v>1.150576509291287</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150196048981315</v>
+        <v>1.150162511545449</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149654295529953</v>
+        <v>1.149614566895159</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148149128172622</v>
+        <v>1.148108505904139</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.145916979197563</v>
+        <v>1.145886562634468</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.142408596533985</v>
+        <v>1.142393791458326</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.139840568275651</v>
+        <v>1.139319186979199</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.138494026315052</v>
+        <v>1.137927606012178</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.138773055098598</v>
+        <v>1.138169292631797</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.13817005156953</v>
+        <v>1.13750152228852</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.138384123701702</v>
+        <v>1.137629853522899</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.138712368192992</v>
+        <v>1.137873430924387</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.138274713810319</v>
+        <v>1.1373540320402</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.130771152408205</v>
+        <v>1.129949497666739</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.123951443717742</v>
+        <v>1.123184469816727</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.10594743842199</v>
+        <v>1.105329602419629</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.084765989132923</v>
+        <v>1.085013770273733</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.081709219504096</v>
+        <v>1.081853700724511</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.076468295649851</v>
+        <v>1.076623920796073</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>46395</v>
       </c>
       <c r="B124">
-        <v>1.092008295649851</v>
+        <v>1.082801454997631</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187221191181136</v>
+        <v>1.187208488710742</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178940499769819</v>
+        <v>1.178920341768842</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177438846978812</v>
+        <v>1.177421233286048</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.173004414487319</v>
+        <v>1.172979618251916</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.17178000980652</v>
+        <v>1.171754049357899</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169763156989036</v>
+        <v>1.169736356646482</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167296014104204</v>
+        <v>1.167268988016535</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165554754810693</v>
+        <v>1.165527875672156</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166537571882313</v>
+        <v>1.166519104302287</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161086803570832</v>
+        <v>1.161089419237631</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161570702708718</v>
+        <v>1.161572343440612</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160921801760176</v>
+        <v>1.160923059005297</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162103151572061</v>
+        <v>1.162112791573818</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159733257518053</v>
+        <v>1.15973798933289</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416854500915</v>
+        <v>1.155416484175668</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148476132287965</v>
+        <v>1.148472883294729</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140280885075</v>
+        <v>1.143140606204592</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137863734413374</v>
+        <v>1.13787093666522</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130097907975341</v>
+        <v>1.130117823303963</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124930836401927</v>
+        <v>1.124956099193912</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129678464945153</v>
+        <v>1.129734262660728</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136673288026759</v>
+        <v>1.136752695350511</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14249095058138</v>
+        <v>1.142624219908254</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145770453537127</v>
+        <v>1.145926223617137</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145549340919613</v>
+        <v>1.145735929514813</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139774467841804</v>
+        <v>1.139970102367458</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138154819678432</v>
+        <v>1.138360829077082</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.137989922762951</v>
+        <v>1.138208265545506</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149821074334454</v>
+        <v>1.149964997816323</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165463347669526</v>
+        <v>1.165559326342217</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.165933990586035</v>
+        <v>1.16602414318622</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180560888722947</v>
+        <v>1.180575989352456</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191743294790944</v>
+        <v>1.191670280646883</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199993125249507</v>
+        <v>1.19990512521576</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211840231082863</v>
+        <v>1.211712183535762</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205805519214565</v>
+        <v>1.20576418813848</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.2066783268604</v>
+        <v>1.206608666458459</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210589243344314</v>
+        <v>1.21043230161953</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216519696207031</v>
+        <v>1.216289618648928</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222800328620548</v>
+        <v>1.222534680553702</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221300203076658</v>
+        <v>1.221095851658335</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208783806918331</v>
+        <v>1.208599884583748</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.20046394692404</v>
+        <v>1.200289883164253</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189723592641815</v>
+        <v>1.189591543644887</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181324339756476</v>
+        <v>1.181213125351408</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.176031411063858</v>
+        <v>1.17594780683411</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172486648434811</v>
+        <v>1.172430575804237</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173875603333399</v>
+        <v>1.17378147453456</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169831690014846</v>
+        <v>1.169771938674715</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168631686948319</v>
+        <v>1.168561947540908</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168818898958186</v>
+        <v>1.168706420499997</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166667226781816</v>
+        <v>1.16657034000574</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158374929994211</v>
+        <v>1.158301671161367</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.152048661735105</v>
+        <v>1.151943088777871</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146490447974909</v>
+        <v>1.147182623587776</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143969609324096</v>
+        <v>1.144411101445789</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144522198810352</v>
+        <v>1.144497224832138</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146615005278867</v>
+        <v>1.145737201695584</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149263191050367</v>
+        <v>1.148261210105702</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150576509291287</v>
+        <v>1.149216751597879</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150162511545449</v>
+        <v>1.148109933846289</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149614566895159</v>
+        <v>1.147215799903294</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148108505904139</v>
+        <v>1.146261160688496</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.145886562634468</v>
+        <v>1.144334985873218</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.142393791458326</v>
+        <v>1.142182192540106</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.139319186979199</v>
+        <v>1.139601018237129</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.137927606012178</v>
+        <v>1.138706516020003</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.138169292631797</v>
+        <v>1.138998765194013</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.13750152228852</v>
+        <v>1.137835874240645</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.137629853522899</v>
+        <v>1.13742614332136</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.137873430924387</v>
+        <v>1.138201435817493</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.1373540320402</v>
+        <v>1.137164850969668</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.129949497666739</v>
+        <v>1.129957331462847</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.123184469816727</v>
+        <v>1.121938301029111</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.105329602419629</v>
+        <v>1.111996881868657</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.085013770273733</v>
+        <v>1.089193434655351</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.081853700724511</v>
+        <v>1.066430133903776</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.076623920796073</v>
+        <v>1.046704622471661</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>46395</v>
       </c>
       <c r="B124">
-        <v>1.082801454997631</v>
+        <v>1.048702336544196</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187208488710742</v>
+        <v>1.18722375735498</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178920341768842</v>
+        <v>1.178944572977334</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177421233286048</v>
+        <v>1.177442408313751</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172979618251916</v>
+        <v>1.173009427036005</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171754049357899</v>
+        <v>1.171785257448054</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169736356646482</v>
+        <v>1.16976857417323</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167268988016535</v>
+        <v>1.167301476805911</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165527875672156</v>
+        <v>1.165560187799253</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166519104302287</v>
+        <v>1.166541309646706</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161089419237631</v>
+        <v>1.161086276644369</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161572343440612</v>
+        <v>1.161570372668018</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160923059005297</v>
+        <v>1.160921549154291</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162112791573818</v>
+        <v>1.16210120681118</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15973798933289</v>
+        <v>1.15973230262184</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416484175668</v>
+        <v>1.155416931376008</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148472883294729</v>
+        <v>1.148476796881588</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140606204592</v>
+        <v>1.143140228937788</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.13787093666522</v>
+        <v>1.137862300297706</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130117823303963</v>
+        <v>1.13009390159111</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124956099193912</v>
+        <v>1.124925747035257</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129734262660728</v>
+        <v>1.12966720927155</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136752695350511</v>
+        <v>1.136657262258402</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142624219908254</v>
+        <v>1.142464013485764</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145926223617137</v>
+        <v>1.145738960006985</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145735929514813</v>
+        <v>1.145511609162498</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139970102367458</v>
+        <v>1.139734887620817</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138360829077082</v>
+        <v>1.138113121974563</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138208265545506</v>
+        <v>1.137945704850511</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149964997816323</v>
+        <v>1.149791907699885</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165559326342217</v>
+        <v>1.165443900728699</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.16602414318622</v>
+        <v>1.165915710815628</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180575989352456</v>
+        <v>1.180557815022494</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191670280646883</v>
+        <v>1.191758094666335</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.19990512521576</v>
+        <v>1.200010957055497</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211712183535762</v>
+        <v>1.211866138367697</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.20576418813848</v>
+        <v>1.205813789993523</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206608666458459</v>
+        <v>1.206692310216967</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.21043230161953</v>
+        <v>1.210620900728384</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216289618648928</v>
+        <v>1.216566196798838</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222534680553702</v>
+        <v>1.22285403095222</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221095851658335</v>
+        <v>1.221341473018064</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208599884583748</v>
+        <v>1.20882097489498</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200289883164253</v>
+        <v>1.200499140494383</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189591543644887</v>
+        <v>1.189750326154306</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181213125351408</v>
+        <v>1.181346865415808</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.17594780683411</v>
+        <v>1.176048351485687</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172430575804237</v>
+        <v>1.172498007852808</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.17378147453456</v>
+        <v>1.173894660228198</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169771938674715</v>
+        <v>1.169843760018133</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168561947540908</v>
+        <v>1.168645772548693</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168706420499997</v>
+        <v>1.168841648499211</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.16657034000574</v>
+        <v>1.166686815927557</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158301671161367</v>
+        <v>1.158389707949004</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151943088777871</v>
+        <v>1.152070045619196</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.147182623587776</v>
+        <v>1.14651219915824</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144411101445789</v>
+        <v>1.143982015294629</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144497224832138</v>
+        <v>1.144518746741712</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.145737201695584</v>
+        <v>1.146597041465969</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.148261210105702</v>
+        <v>1.149225411939326</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.149216751597879</v>
+        <v>1.150524054193197</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.148109933846289</v>
+        <v>1.150096971631469</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.147215799903294</v>
+        <v>1.149536868003507</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.146261160688496</v>
+        <v>1.148028949264409</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.144334985873218</v>
+        <v>1.14582681158428</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.142182192540106</v>
+        <v>1.142364428404834</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.139601018237129</v>
+        <v>1.138479516849058</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.138706516020003</v>
+        <v>1.137068181432552</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.138998765194013</v>
+        <v>1.137263328776524</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.137835874240645</v>
+        <v>1.13653910306967</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.13742614332136</v>
+        <v>1.136580729961565</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.138201435817493</v>
+        <v>1.136697365435807</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.137164850969668</v>
+        <v>1.136038484475862</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.129957331462847</v>
+        <v>1.12883056479342</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.121938301029111</v>
+        <v>1.122202344822995</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.111996881868657</v>
+        <v>1.104963411705733</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.089193434655351</v>
+        <v>1.086380405866461</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.066430133903776</v>
+        <v>1.083355011342289</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.046704622471661</v>
+        <v>1.07889069534869</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>46395</v>
       </c>
       <c r="B124">
-        <v>1.048702336544196</v>
+        <v>1.082416259020526</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.18722375735498</v>
+        <v>1.18721000180973</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178944572977334</v>
+        <v>1.178922742589426</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177442408313751</v>
+        <v>1.177423330110624</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.173009427036005</v>
+        <v>1.172982570569787</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171785257448054</v>
+        <v>1.171757140399651</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.16976857417323</v>
+        <v>1.169739547792982</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167301476805911</v>
+        <v>1.167272206091405</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165560187799253</v>
+        <v>1.165531076254022</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166541309646706</v>
+        <v>1.166521301143368</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161086276644369</v>
+        <v>1.161089107017411</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161570372668018</v>
+        <v>1.161572147384275</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160921549154291</v>
+        <v>1.160922908645619</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.16210120681118</v>
+        <v>1.162111642093619</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.15973230262184</v>
+        <v>1.159737425241304</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416931376008</v>
+        <v>1.155416527396383</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148476796881588</v>
+        <v>1.148473266753524</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140228937788</v>
+        <v>1.14314056150184</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137862300297706</v>
+        <v>1.137870069720061</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.13009390159111</v>
+        <v>1.130115443706675</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124925747035257</v>
+        <v>1.124953083774259</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.12966720927155</v>
+        <v>1.1297276089449</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136657262258402</v>
+        <v>1.136743229503428</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142464013485764</v>
+        <v>1.142608351089292</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145738960006985</v>
+        <v>1.145907679234101</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145511609162498</v>
+        <v>1.145713719387626</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139734887620817</v>
+        <v>1.139946823792964</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138113121974563</v>
+        <v>1.138336323987146</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.137945704850511</v>
+        <v>1.138182303697013</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149791907699885</v>
+        <v>1.149947893224611</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165443900728699</v>
+        <v>1.165547918223521</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.165915710815628</v>
+        <v>1.166013433300824</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180557815022494</v>
+        <v>1.180574200495578</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191758094666335</v>
+        <v>1.191678956608087</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.200010957055497</v>
+        <v>1.199915584341668</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211866138367697</v>
+        <v>1.211727419516816</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205813789993523</v>
+        <v>1.205769145514363</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206692310216967</v>
+        <v>1.206617002902084</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210620900728384</v>
+        <v>1.210451016983362</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216566196798838</v>
+        <v>1.216317016396567</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.22285403095222</v>
+        <v>1.222566308553464</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221341473018064</v>
+        <v>1.221120199351542</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.20882097489498</v>
+        <v>1.208621787921903</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200499140494383</v>
+        <v>1.200310604703022</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189750326154306</v>
+        <v>1.18960724847961</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181346865415808</v>
+        <v>1.181226347926319</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.176048351485687</v>
+        <v>1.17595774378441</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172498007852808</v>
+        <v>1.172437241452388</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173894660228198</v>
+        <v>1.173792669320197</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169843760018133</v>
+        <v>1.169779056554311</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168645772548693</v>
+        <v>1.168570256125573</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168841648499211</v>
+        <v>1.168719807255077</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166686815927557</v>
+        <v>1.16658187408294</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158389707949004</v>
+        <v>1.158310407017087</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.152070045619196</v>
+        <v>1.151955640123855</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14651219915824</v>
+        <v>1.14719498006985</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143982015294629</v>
+        <v>1.14441776782733</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144518746741712</v>
+        <v>1.144495671031097</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146597041465969</v>
+        <v>1.145728710899326</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149225411939326</v>
+        <v>1.148242014682685</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150524054193197</v>
+        <v>1.149189598499909</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150096971631469</v>
+        <v>1.148075545307598</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149536868003507</v>
+        <v>1.147173853217327</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.148028949264409</v>
+        <v>1.146216587503592</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.14582681158428</v>
+        <v>1.1442985184863</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.142364428404834</v>
+        <v>1.142158672373562</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.138479516849058</v>
+        <v>1.139064500520309</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.137068181432552</v>
+        <v>1.138066001437324</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.137263328776524</v>
+        <v>1.13825489735765</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.13653910306967</v>
+        <v>1.136761814906322</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.136580729961565</v>
+        <v>1.136275866574517</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.136697365435807</v>
+        <v>1.136799870857713</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.136038484475862</v>
+        <v>1.135552410153101</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.12883056479342</v>
+        <v>1.128258125280512</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.122202344822995</v>
+        <v>1.120154089532146</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.104963411705733</v>
+        <v>1.109998535792634</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.086380405866461</v>
+        <v>1.087776489803135</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.083355011342289</v>
+        <v>1.065763829549547</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.07889069534869</v>
+        <v>1.046984816908577</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>46395</v>
       </c>
       <c r="B124">
-        <v>1.082416259020526</v>
+        <v>1.047048659069205</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.18721000180973</v>
+        <v>1.187225008892728</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178922742589426</v>
+        <v>1.178946559608236</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177423330110624</v>
+        <v>1.177444145561418</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172982570569787</v>
+        <v>1.17301187207134</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171757140399651</v>
+        <v>1.171787817126874</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169739547792982</v>
+        <v>1.169771216522603</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167272206091405</v>
+        <v>1.167304141343713</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165531076254022</v>
+        <v>1.165562837842586</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166521301143368</v>
+        <v>1.166543133418442</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161089107017411</v>
+        <v>1.16108601984157</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161572147384275</v>
+        <v>1.161570211878711</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160922908645619</v>
+        <v>1.160921426125766</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162111642093619</v>
+        <v>1.162100258673105</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159737425241304</v>
+        <v>1.159731837039833</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.155416527396383</v>
+        <v>1.15541696911942</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148473266753524</v>
+        <v>1.148477122010381</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14314056150184</v>
+        <v>1.143140205282726</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137870069720061</v>
+        <v>1.137861603420927</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130115443706675</v>
+        <v>1.130091949723119</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124953083774259</v>
+        <v>1.12492326666437</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.1297276089449</v>
+        <v>1.129661721857129</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136743229503428</v>
+        <v>1.136649448393382</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142608351089292</v>
+        <v>1.14245087444386</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145907679234101</v>
+        <v>1.145723597458355</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145713719387626</v>
+        <v>1.145493202714787</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139946823792964</v>
+        <v>1.139715577113931</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138336323987146</v>
+        <v>1.13809277613956</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138182303697013</v>
+        <v>1.137924126414119</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149947893224611</v>
+        <v>1.149777671885105</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165547918223521</v>
+        <v>1.165434409375674</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166013433300824</v>
+        <v>1.165906787499275</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180574200495578</v>
+        <v>1.180556313133306</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191678956608087</v>
+        <v>1.191765318675901</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199915584341668</v>
+        <v>1.200019660296476</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211727419516816</v>
+        <v>1.211878778232371</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205769145514363</v>
+        <v>1.205817814049793</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206617002902084</v>
+        <v>1.20669911902866</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210451016983362</v>
+        <v>1.210636334286545</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216317016396567</v>
+        <v>1.216588877795885</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222566308553464</v>
+        <v>1.222880226177765</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221120199351542</v>
+        <v>1.221361598910815</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208621787921903</v>
+        <v>1.208839103301222</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200310604703022</v>
+        <v>1.200516308069445</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.18960724847961</v>
+        <v>1.189763371124027</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181226347926319</v>
+        <v>1.181357858348463</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.17595774378441</v>
+        <v>1.176056619587998</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172437241452388</v>
+        <v>1.172503551747256</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173792669320197</v>
+        <v>1.17390395934989</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169779056554311</v>
+        <v>1.169849646476033</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168570256125573</v>
+        <v>1.168652641751257</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168719807255077</v>
+        <v>1.168852746782234</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.16658187408294</v>
+        <v>1.166696371591423</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158310407017087</v>
+        <v>1.158396912538254</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151955640123855</v>
+        <v>1.152080481404483</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.14719498006985</v>
+        <v>1.146522821293545</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.14441776782733</v>
+        <v>1.143988086127845</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144495671031097</v>
+        <v>1.144517087199144</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.145728710899326</v>
+        <v>1.146588295528074</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.148242014682685</v>
+        <v>1.149206990539277</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.149189598499909</v>
+        <v>1.150498447178195</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.148075545307598</v>
+        <v>1.150064946387966</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.147173853217327</v>
+        <v>1.149498872739549</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.146216587503592</v>
+        <v>1.147989992840981</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.1442985184863</v>
+        <v>1.145797466216627</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.142158672373562</v>
+        <v>1.142349873797273</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.139064500520309</v>
+        <v>1.138036394633938</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.138066001437324</v>
+        <v>1.136598898832226</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.13825489735765</v>
+        <v>1.136771981508379</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.136761814906322</v>
+        <v>1.136006029628676</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.136275866574517</v>
+        <v>1.135974694877965</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.136799870857713</v>
+        <v>1.136014668170328</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.135552410153101</v>
+        <v>1.135271671307456</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.128258125280512</v>
+        <v>1.128130573783358</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.120154089532146</v>
+        <v>1.121531834395304</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.109998535792634</v>
+        <v>1.104815719398318</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.087776489803135</v>
+        <v>1.086628408988654</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.065763829549547</v>
+        <v>1.083522111988565</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.046984816908577</v>
+        <v>1.079011220664424</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>46395</v>
       </c>
       <c r="B124">
-        <v>1.047048659069205</v>
+        <v>1.080771575182275</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.136598898832226</v>
+        <v>1.136600431050019</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.136771981508379</v>
+        <v>1.136774159928406</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.136006029628676</v>
+        <v>1.135985886114816</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.135974694877965</v>
+        <v>1.135975460165212</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.136014668170328</v>
+        <v>1.136015553529439</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.135271671307456</v>
+        <v>1.135272695761369</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.128130573783358</v>
+        <v>1.128131734698838</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.121531834395304</v>
+        <v>1.121533122433919</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.104815719398318</v>
+        <v>1.104818309495958</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.086628408988654</v>
+        <v>1.086628458447689</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.083522111988565</v>
+        <v>1.083522155087363</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.079011220664424</v>
+        <v>1.079011265135428</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>46395</v>
       </c>
       <c r="B124">
-        <v>1.080771575182275</v>
+        <v>1.080771640451074</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B124"/>
+  <dimension ref="A1:B125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187225008892728</v>
+        <v>1.187211487891267</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178946559608236</v>
+        <v>1.178925100639104</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177444145561418</v>
+        <v>1.177425389835102</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.17301187207134</v>
+        <v>1.172985470533341</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171787817126874</v>
+        <v>1.171760176598362</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169771216522603</v>
+        <v>1.169742682293783</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167304141343713</v>
+        <v>1.167275367029764</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165562837842586</v>
+        <v>1.165534220008734</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166543133418442</v>
+        <v>1.166523459545461</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.16108601984157</v>
+        <v>1.161088800542163</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161570211878711</v>
+        <v>1.161571954990543</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160921426125766</v>
+        <v>1.160922761128319</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162100258673105</v>
+        <v>1.162110513448086</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159731837039833</v>
+        <v>1.159736871338879</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541696911942</v>
+        <v>1.15541657008036</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148477122010381</v>
+        <v>1.148473644301899</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140205282726</v>
+        <v>1.143140519163814</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137861603420927</v>
+        <v>1.137869220629448</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130091949723119</v>
+        <v>1.13011310852269</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.12492326666437</v>
+        <v>1.124950123815452</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129661721857129</v>
+        <v>1.129721075920048</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136649448393382</v>
+        <v>1.136733934501442</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.14245087444386</v>
+        <v>1.142592764024193</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145723597458355</v>
+        <v>1.145889463139024</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145493202714787</v>
+        <v>1.14569190159922</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139715577113931</v>
+        <v>1.139923954238373</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.13809277613956</v>
+        <v>1.138312247359475</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.137924126414119</v>
+        <v>1.138156793061065</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149777671885105</v>
+        <v>1.149931083679183</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165434409375674</v>
+        <v>1.165536707296581</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.165906787499275</v>
+        <v>1.166002907024161</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180556313133306</v>
+        <v>1.180572440981433</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191765318675901</v>
+        <v>1.191687483282183</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.200019660296476</v>
+        <v>1.199925862850439</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211878778232371</v>
+        <v>1.211742387890554</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205817814049793</v>
+        <v>1.205774005410647</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.20669911902866</v>
+        <v>1.206625180347843</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210636334286545</v>
+        <v>1.210469392746973</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216588877795885</v>
+        <v>1.216343927262105</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222880226177765</v>
+        <v>1.222597375951588</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221361598910815</v>
+        <v>1.221144110837857</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208839103301222</v>
+        <v>1.208643301562319</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200516308069445</v>
+        <v>1.200330959612204</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189763371124027</v>
+        <v>1.189622679401776</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181357858348463</v>
+        <v>1.181239341029257</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.176056619587998</v>
+        <v>1.175967509059991</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172503551747256</v>
+        <v>1.172443791673399</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.17390395934989</v>
+        <v>1.173803668881614</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169849646476033</v>
+        <v>1.16978604724881</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168652641751257</v>
+        <v>1.168578416018717</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168852746782234</v>
+        <v>1.168732958023642</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166696371591423</v>
+        <v>1.166593204044079</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158396912538254</v>
+        <v>1.158318984437567</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.152080481404483</v>
+        <v>1.151967973803543</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146522821293545</v>
+        <v>1.147207127462462</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143988086127845</v>
+        <v>1.144424333866059</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144517087199144</v>
+        <v>1.144494166462377</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146588295528074</v>
+        <v>1.145720386920487</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149206990539277</v>
+        <v>1.148223168027651</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150498447178195</v>
+        <v>1.149162916035515</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150064946387966</v>
+        <v>1.148041734608002</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149498872739549</v>
+        <v>1.147132594570375</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.147989992840981</v>
+        <v>1.146172704729573</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.145797466216627</v>
+        <v>1.144262560032827</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.142349873797273</v>
+        <v>1.142135405486948</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.138036394633938</v>
+        <v>1.139060347001055</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.136600431050019</v>
+        <v>1.13757528400642</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.136774159928406</v>
+        <v>1.137688781482148</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.135985886114816</v>
+        <v>1.13624013903772</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.135975460165212</v>
+        <v>1.135673734015953</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.136015553529439</v>
+        <v>1.135771229301852</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.135272695761369</v>
+        <v>1.134732976638599</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.128131734698838</v>
+        <v>1.127512409899679</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.121533122433919</v>
+        <v>1.119517407447061</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.104818309495958</v>
+        <v>1.109600462251238</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.086628458447689</v>
+        <v>1.088260150013998</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.083522155087363</v>
+        <v>1.067494555012748</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.079011265135428</v>
+        <v>1.050567290256909</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1378,7 +1378,15 @@
         <v>46395</v>
       </c>
       <c r="B124">
-        <v>1.080771640451074</v>
+        <v>1.052116065179753</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B125">
+        <v>1.067656065179753</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187211487891267</v>
+        <v>1.187226240081625</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178925100639104</v>
+        <v>1.178948514004964</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177425389835102</v>
+        <v>1.177445854795943</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172985470533341</v>
+        <v>1.173014277599838</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171760176598362</v>
+        <v>1.171790335426762</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169742682293783</v>
+        <v>1.169773816138413</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167275367029764</v>
+        <v>1.167306762780326</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165534220008734</v>
+        <v>1.165565445018355</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166523459545461</v>
+        <v>1.166544928076229</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161088800542163</v>
+        <v>1.16108576733075</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161571954990543</v>
+        <v>1.16157005381464</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160922761128319</v>
+        <v>1.160921305205562</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162110513448086</v>
+        <v>1.162099326163976</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159736871338879</v>
+        <v>1.159731379108688</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541657008036</v>
+        <v>1.15541700640965</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148473644301899</v>
+        <v>1.14847744249422</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140519163814</v>
+        <v>1.143140183087043</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137869220629448</v>
+        <v>1.137860919506187</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.13011310852269</v>
+        <v>1.130090030914606</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124950123815452</v>
+        <v>1.124920827737407</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129721075920048</v>
+        <v>1.129656324971411</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136733934501442</v>
+        <v>1.136641762853527</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142592764024193</v>
+        <v>1.142437947968859</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145889463139024</v>
+        <v>1.145708482794175</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.14569190159922</v>
+        <v>1.145475092697783</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139923954238373</v>
+        <v>1.139696576105204</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138312247359475</v>
+        <v>1.138072754961631</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138156793061065</v>
+        <v>1.13790289044994</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149931083679183</v>
+        <v>1.149763660446575</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165536707296581</v>
+        <v>1.165425067886254</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.166002907024161</v>
+        <v>1.165898004043434</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180572440981433</v>
+        <v>1.180554833850981</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191687483282183</v>
+        <v>1.191772429083596</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199925862850439</v>
+        <v>1.200028226230607</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211742387890554</v>
+        <v>1.211891215609905</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205774005410647</v>
+        <v>1.205821766501544</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206625180347843</v>
+        <v>1.206705810122903</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210469392746973</v>
+        <v>1.210651513106165</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216343927262105</v>
+        <v>1.21661119154224</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222597375951588</v>
+        <v>1.222905998225284</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221144110837857</v>
+        <v>1.221381396480297</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208643301562319</v>
+        <v>1.208856937822121</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200330959612204</v>
+        <v>1.200533198722855</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189622679401776</v>
+        <v>1.189776208389452</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181239341029257</v>
+        <v>1.181368677044036</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175967509059991</v>
+        <v>1.176064757199287</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172443791673399</v>
+        <v>1.172509007959439</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173803668881614</v>
+        <v>1.173913110449296</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.16978604724881</v>
+        <v>1.169855437123743</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168578416018717</v>
+        <v>1.168659398989207</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168732958023642</v>
+        <v>1.1688636666602</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166593204044079</v>
+        <v>1.166705773117104</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158318984437567</v>
+        <v>1.158403998251197</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151967973803543</v>
+        <v>1.152090751812886</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.147207127462462</v>
+        <v>1.146533279639429</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144424333866059</v>
+        <v>1.143994071284796</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144494166462377</v>
+        <v>1.144515470057482</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.145720386920487</v>
+        <v>1.146579701537089</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.148223168027651</v>
+        <v>1.149188871138115</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.149162916035515</v>
+        <v>1.150473241084848</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.148041734608002</v>
+        <v>1.150033402988704</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.147132594570375</v>
+        <v>1.149461430826421</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.146172704729573</v>
+        <v>1.147951570089475</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.144262560032827</v>
+        <v>1.145768467150813</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.142135405486948</v>
+        <v>1.142335405777502</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.139060347001055</v>
+        <v>1.138037801638837</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.13757528400642</v>
+        <v>1.136204515211263</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.137688781482148</v>
+        <v>1.136335013848871</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.13624013903772</v>
+        <v>1.135543236555447</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.135673734015953</v>
+        <v>1.135442758316075</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.135771229301852</v>
+        <v>1.135473156130471</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.134732976638599</v>
+        <v>1.134650945285815</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.127512409899679</v>
+        <v>1.127597051824484</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.119517407447061</v>
+        <v>1.121064709832419</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.109600462251238</v>
+        <v>1.104841769922906</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.088260150013998</v>
+        <v>1.087406135037028</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.067494555012748</v>
+        <v>1.084316777173449</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.050567290256909</v>
+        <v>1.079987495706246</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>46395</v>
       </c>
       <c r="B124">
-        <v>1.052116065179753</v>
+        <v>1.081252054035541</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -1386,7 +1386,7 @@
         <v>46402</v>
       </c>
       <c r="B125">
-        <v>1.067656065179753</v>
+        <v>1.078694299202926</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187226240081625</v>
+        <v>1.187212947672554</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178948514004964</v>
+        <v>1.178927417050671</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177445854795943</v>
+        <v>1.177427413435329</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.173014277599838</v>
+        <v>1.172988319522766</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171790335426762</v>
+        <v>1.171763159400582</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169773816138413</v>
+        <v>1.169745761643684</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167306762780326</v>
+        <v>1.167278472339699</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165565445018355</v>
+        <v>1.16553730843625</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166544928076229</v>
+        <v>1.166525580508118</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.16108576733075</v>
+        <v>1.161088499654904</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.16157005381464</v>
+        <v>1.161571766157921</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160921305205562</v>
+        <v>1.160922616373781</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162099326163976</v>
+        <v>1.162109405076071</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159731379108688</v>
+        <v>1.159736327352164</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541700640965</v>
+        <v>1.155416612235567</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.14847744249422</v>
+        <v>1.148474016071981</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.143140183087043</v>
+        <v>1.143140479086583</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137860919506187</v>
+        <v>1.137868388857345</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130090030914606</v>
+        <v>1.130110816523019</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124920827737407</v>
+        <v>1.124947217803413</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129656324971411</v>
+        <v>1.129714660335006</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136641762853527</v>
+        <v>1.136724805765022</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142437947968859</v>
+        <v>1.14257745128</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145708482794175</v>
+        <v>1.14587156669848</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145475092697783</v>
+        <v>1.145670465855299</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139696576105204</v>
+        <v>1.139901483031291</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138072754961631</v>
+        <v>1.138288588071762</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.13790289044994</v>
+        <v>1.138131721998697</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149763660446575</v>
+        <v>1.149914561624128</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165425067886254</v>
+        <v>1.165525688498877</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.165898004043434</v>
+        <v>1.165992559683318</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180554833850981</v>
+        <v>1.18057071009525</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191772429083596</v>
+        <v>1.191695864483212</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.200028226230607</v>
+        <v>1.199935965373899</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211891215609905</v>
+        <v>1.211757095641084</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205821766501544</v>
+        <v>1.205778770646506</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206705810122903</v>
+        <v>1.206633203275685</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210651513106165</v>
+        <v>1.210487438056461</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.21661119154224</v>
+        <v>1.216370364099016</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222905998225284</v>
+        <v>1.222627897506067</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221381396480297</v>
+        <v>1.221167597722351</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208856937822121</v>
+        <v>1.208664435799677</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200533198722855</v>
+        <v>1.200350957521416</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189776208389452</v>
+        <v>1.189637843501874</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181368677044036</v>
+        <v>1.181252110570965</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.176064757199287</v>
+        <v>1.175977107065668</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172509007959439</v>
+        <v>1.17245022943581</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173913110449296</v>
+        <v>1.17381447827461</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169855437123743</v>
+        <v>1.169792914131277</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168659398989207</v>
+        <v>1.168586431169733</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.1688636666602</v>
+        <v>1.168745878983913</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166705773117104</v>
+        <v>1.166604335255333</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158403998251197</v>
+        <v>1.158327407685289</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.152090751812886</v>
+        <v>1.151980095408573</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.146533279639429</v>
+        <v>1.147219070997575</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.143994071284796</v>
+        <v>1.144430801732796</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144515470057482</v>
+        <v>1.144492709286644</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.146579701537089</v>
+        <v>1.145712224999909</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.149188871138115</v>
+        <v>1.148204660838684</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.150473241084848</v>
+        <v>1.149136692229594</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.150033402988704</v>
+        <v>1.148008487537381</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.149461430826421</v>
+        <v>1.147092007529313</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.147951570089475</v>
+        <v>1.146129497031956</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.145768467150813</v>
+        <v>1.144227100786693</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.142335405777502</v>
+        <v>1.142112389414773</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.138037801638837</v>
+        <v>1.139056112257881</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.136204515211263</v>
+        <v>1.137127660414404</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.136335013848871</v>
+        <v>1.137169769095757</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.135543236555447</v>
+        <v>1.135771315150292</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.135442758316075</v>
+        <v>1.135143244859087</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.135473156130471</v>
+        <v>1.134873358799877</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.134650945285815</v>
+        <v>1.134019968958521</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.127597051824484</v>
+        <v>1.126890103380188</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.121064709832419</v>
+        <v>1.119027255338659</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.104841769922906</v>
+        <v>1.109370387591443</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.087406135037028</v>
+        <v>1.088901880659096</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.084316777173449</v>
+        <v>1.069296862753612</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.079987495706246</v>
+        <v>1.053957625519381</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>46395</v>
       </c>
       <c r="B124">
-        <v>1.081252054035541</v>
+        <v>1.056450182130696</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -1386,7 +1386,7 @@
         <v>46402</v>
       </c>
       <c r="B125">
-        <v>1.078694299202926</v>
+        <v>1.071990182130697</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -399,114 +399,994 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3">
-        <v>46304</v>
+        <v>44743</v>
       </c>
       <c r="B2">
-        <v>1.11895</v>
+        <v>1.05615</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3">
-        <v>46311</v>
+        <v>44778</v>
       </c>
       <c r="B3">
-        <v>1.118177812341526</v>
+        <v>1.059572113940927</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3">
-        <v>46318</v>
+        <v>44806</v>
       </c>
       <c r="B4">
-        <v>1.117951177116157</v>
+        <v>1.05809387751325</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3">
-        <v>46325</v>
+        <v>44834</v>
       </c>
       <c r="B5">
-        <v>1.117779580247386</v>
+        <v>1.022349949106381</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3">
-        <v>46332</v>
+        <v>44869</v>
       </c>
       <c r="B6">
-        <v>1.118757737712577</v>
+        <v>1.023554358197345</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3">
-        <v>46339</v>
+        <v>44897</v>
       </c>
       <c r="B7">
-        <v>1.119825685029435</v>
+        <v>1.017177216748039</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3">
-        <v>46346</v>
+        <v>44932</v>
       </c>
       <c r="B8">
-        <v>1.119975929024421</v>
+        <v>1.035437635969992</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3">
-        <v>46353</v>
+        <v>44960</v>
       </c>
       <c r="B9">
-        <v>1.119092576345834</v>
+        <v>1.033669605731821</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3">
-        <v>46360</v>
+        <v>44988</v>
       </c>
       <c r="B10">
-        <v>1.11703547383422</v>
+        <v>1.020812503881198</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3">
-        <v>46367</v>
+        <v>45016</v>
       </c>
       <c r="B11">
-        <v>1.119418800810793</v>
+        <v>1.0369453589657</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3">
-        <v>46374</v>
+        <v>45051</v>
       </c>
       <c r="B12">
-        <v>1.091195947010269</v>
+        <v>1.065123336648514</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3">
-        <v>46381</v>
+        <v>45079</v>
       </c>
       <c r="B13">
-        <v>1.085971144121937</v>
+        <v>1.066625859070529</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3">
-        <v>46388</v>
+        <v>45107</v>
       </c>
       <c r="B14">
-        <v>1.080208739090724</v>
+        <v>1.070569711760595</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3">
+        <v>45114</v>
+      </c>
+      <c r="B15">
+        <v>1.070569711760595</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3">
+        <v>45121</v>
+      </c>
+      <c r="B16">
+        <v>1.070569711760595</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3">
+        <v>45128</v>
+      </c>
+      <c r="B17">
+        <v>1.070569711760595</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3">
+        <v>45135</v>
+      </c>
+      <c r="B18">
+        <v>1.070569711760595</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="3">
+        <v>45142</v>
+      </c>
+      <c r="B19">
+        <v>1.071663685426455</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="3">
+        <v>45170</v>
+      </c>
+      <c r="B20">
+        <v>1.06690090021214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3">
+        <v>45205</v>
+      </c>
+      <c r="B21">
+        <v>1.062072760998838</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="3">
+        <v>45233</v>
+      </c>
+      <c r="B22">
+        <v>1.069584322347632</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="3">
+        <v>45261</v>
+      </c>
+      <c r="B23">
+        <v>1.065835177815887</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="3">
+        <v>45296</v>
+      </c>
+      <c r="B24">
+        <v>1.076523142912448</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="3">
+        <v>45324</v>
+      </c>
+      <c r="B25">
+        <v>1.081237204891821</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="3">
+        <v>45352</v>
+      </c>
+      <c r="B26">
+        <v>1.077788896093836</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="3">
+        <v>45387</v>
+      </c>
+      <c r="B27">
+        <v>1.080708117949502</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="3">
+        <v>45415</v>
+      </c>
+      <c r="B28">
+        <v>1.086907148496961</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="3">
+        <v>45443</v>
+      </c>
+      <c r="B29">
+        <v>1.081972933789708</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="3">
+        <v>45478</v>
+      </c>
+      <c r="B30">
+        <v>1.08039328716012</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="3">
+        <v>45506</v>
+      </c>
+      <c r="B31">
+        <v>1.078278421441137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="3">
+        <v>45541</v>
+      </c>
+      <c r="B32">
+        <v>1.076889892112673</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3">
+        <v>45569</v>
+      </c>
+      <c r="B33">
+        <v>1.093052866142771</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="3">
+        <v>45597</v>
+      </c>
+      <c r="B34">
+        <v>1.080030202865601</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="3">
+        <v>45632</v>
+      </c>
+      <c r="B35">
+        <v>1.055520415306091</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="3">
+        <v>45660</v>
+      </c>
+      <c r="B36">
+        <v>1.036494970321655</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3">
+        <v>45688</v>
+      </c>
+      <c r="B37">
+        <v>1.030573574973704</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3">
+        <v>45716</v>
+      </c>
+      <c r="B38">
+        <v>1.032524466514587</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3">
+        <v>45751</v>
+      </c>
+      <c r="B39">
+        <v>1.096287292864</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3">
+        <v>45779</v>
+      </c>
+      <c r="B40">
+        <v>1.1119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3">
+        <v>45814</v>
+      </c>
+      <c r="B41">
+        <v>1.1377</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3">
+        <v>45821</v>
+      </c>
+      <c r="B42">
+        <v>1.17669412317029</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="3">
+        <v>45828</v>
+      </c>
+      <c r="B43">
+        <v>1.16455129878198</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="3">
+        <v>45835</v>
+      </c>
+      <c r="B44">
+        <v>1.17373864139101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3">
+        <v>45842</v>
+      </c>
+      <c r="B45">
+        <v>1.18453374331697</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3">
+        <v>45849</v>
+      </c>
+      <c r="B46">
+        <v>1.187214381845632</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3">
+        <v>45856</v>
+      </c>
+      <c r="B47">
+        <v>1.178929692917275</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3">
+        <v>45863</v>
+      </c>
+      <c r="B48">
+        <v>1.177429401853231</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3">
+        <v>45870</v>
+      </c>
+      <c r="B49">
+        <v>1.172991118870165</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3">
+        <v>45877</v>
+      </c>
+      <c r="B50">
+        <v>1.171766090202442</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3">
+        <v>45884</v>
+      </c>
+      <c r="B51">
+        <v>1.169748787285354</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3">
+        <v>45891</v>
+      </c>
+      <c r="B52">
+        <v>1.167281523476696</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3">
+        <v>45898</v>
+      </c>
+      <c r="B53">
+        <v>1.165540342984204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="3">
+        <v>45905</v>
+      </c>
+      <c r="B54">
+        <v>1.166527664996555</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3">
+        <v>45912</v>
+      </c>
+      <c r="B55">
+        <v>1.161088204204312</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3">
+        <v>45919</v>
+      </c>
+      <c r="B56">
+        <v>1.161571580788622</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3">
+        <v>45926</v>
+      </c>
+      <c r="B57">
+        <v>1.160922474305333</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="3">
+        <v>45933</v>
+      </c>
+      <c r="B58">
+        <v>1.162108316436391</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3">
+        <v>45940</v>
+      </c>
+      <c r="B59">
+        <v>1.159735793017401</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3">
+        <v>45947</v>
+      </c>
+      <c r="B60">
+        <v>1.15541665386992</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3">
+        <v>45954</v>
+      </c>
+      <c r="B61">
+        <v>1.148474382192126</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="3">
+        <v>45961</v>
+      </c>
+      <c r="B62">
+        <v>1.14314044117129</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="3">
+        <v>45968</v>
+      </c>
+      <c r="B63">
+        <v>1.137867573888667</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3">
+        <v>45975</v>
+      </c>
+      <c r="B64">
+        <v>1.130108566523507</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="3">
+        <v>45982</v>
+      </c>
+      <c r="B65">
+        <v>1.124944364278611</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3">
+        <v>45989</v>
+      </c>
+      <c r="B66">
+        <v>1.129708359054241</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3">
+        <v>45996</v>
+      </c>
+      <c r="B67">
+        <v>1.136715838876715</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3">
+        <v>46003</v>
+      </c>
+      <c r="B68">
+        <v>1.142562405682758</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3">
+        <v>46010</v>
+      </c>
+      <c r="B69">
+        <v>1.145853981578876</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3">
+        <v>46017</v>
+      </c>
+      <c r="B70">
+        <v>1.145649402218214</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3">
+        <v>46024</v>
+      </c>
+      <c r="B71">
+        <v>1.139879399866936</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3">
+        <v>46031</v>
+      </c>
+      <c r="B72">
+        <v>1.138265335382742</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3">
+        <v>46038</v>
+      </c>
+      <c r="B73">
+        <v>1.138107079267037</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B74">
+        <v>1.149898319758895</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B75">
+        <v>1.165514856939492</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46059</v>
+      </c>
+      <c r="B76">
+        <v>1.165982386762319</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46066</v>
+      </c>
+      <c r="B77">
+        <v>1.180569007145244</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46073</v>
+      </c>
+      <c r="B78">
+        <v>1.191704103896605</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B79">
+        <v>1.199945896387072</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B80">
+        <v>1.211771549511749</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46094</v>
+      </c>
+      <c r="B81">
+        <v>1.205783443934319</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46101</v>
+      </c>
+      <c r="B82">
+        <v>1.206641075999651</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B83">
+        <v>1.210505161732895</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46115</v>
+      </c>
+      <c r="B84">
+        <v>1.216396339312654</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
+        <v>46122</v>
+      </c>
+      <c r="B85">
+        <v>1.222657887461944</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3">
+        <v>46129</v>
+      </c>
+      <c r="B86">
+        <v>1.221190671202506</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3">
+        <v>46136</v>
+      </c>
+      <c r="B87">
+        <v>1.208685200569686</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B88">
+        <v>1.200370607726499</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B89">
+        <v>1.189652747628241</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B90">
+        <v>1.181264662261313</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B91">
+        <v>1.175986542057045</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B92">
+        <v>1.172456557607374</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B93">
+        <v>1.173825102382142</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B94">
+        <v>1.169799660456743</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B95">
+        <v>1.168594305389605</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B96">
+        <v>1.168758576100567</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B97">
+        <v>1.166615272896566</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B98">
+        <v>1.158335680871494</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B99">
+        <v>1.151992010341455</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B100">
+        <v>1.147230815735125</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B101">
+        <v>1.144437173539274</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B102">
+        <v>1.144491297746339</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B103">
+        <v>1.145704220554451</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B104">
+        <v>1.148186484137866</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B105">
+        <v>1.149110915504545</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B106">
+        <v>1.147975790339576</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B107">
+        <v>1.147052076167456</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B108">
+        <v>1.146086949505148</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B109">
+        <v>1.144192131232954</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B110">
+        <v>1.14208962163806</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B111">
+        <v>1.139051802135432</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B112">
+        <v>1.136728109692018</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B113">
+        <v>1.136700848831051</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B114">
+        <v>1.135357424619963</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B115">
+        <v>1.134686888347948</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B116">
+        <v>1.134324572530685</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B117">
+        <v>1.133394978255714</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B118">
+        <v>1.126365733788096</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B119">
+        <v>1.118654826940057</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B120">
+        <v>1.109277478516669</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B121">
+        <v>1.089668151155079</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B122">
+        <v>1.071149329840895</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B123">
+        <v>1.05719201733495</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="3">
         <v>46395</v>
       </c>
-      <c r="B15">
-        <v>1.074527227916362</v>
+      <c r="B124">
+        <v>1.060314932764205</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B125">
+        <v>1.075449103162515</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/EURUSD_forecast.xlsx
+++ b/public/data/files/EURUSD_forecast.xlsx
@@ -754,7 +754,7 @@
         <v>45849</v>
       </c>
       <c r="B46">
-        <v>1.187214381845632</v>
+        <v>1.187215791078471</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45856</v>
       </c>
       <c r="B47">
-        <v>1.178929692917275</v>
+        <v>1.178931929294131</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45863</v>
       </c>
       <c r="B48">
-        <v>1.177429401853231</v>
+        <v>1.177431355998277</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45870</v>
       </c>
       <c r="B49">
-        <v>1.172991118870165</v>
+        <v>1.172993869861634</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45877</v>
       </c>
       <c r="B50">
-        <v>1.171766090202442</v>
+        <v>1.171768970351826</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45884</v>
       </c>
       <c r="B51">
-        <v>1.169748787285354</v>
+        <v>1.169751760611588</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45891</v>
       </c>
       <c r="B52">
-        <v>1.167281523476696</v>
+        <v>1.167284521845909</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45898</v>
       </c>
       <c r="B53">
-        <v>1.165540342984204</v>
+        <v>1.165543325050171</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45905</v>
       </c>
       <c r="B54">
-        <v>1.166527664996555</v>
+        <v>1.16652971394311</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45912</v>
       </c>
       <c r="B55">
-        <v>1.161088204204312</v>
+        <v>1.161087914044479</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45919</v>
       </c>
       <c r="B56">
-        <v>1.161571580788622</v>
+        <v>1.161571398788402</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45926</v>
       </c>
       <c r="B57">
-        <v>1.160922474305333</v>
+        <v>1.160922334849102</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45933</v>
       </c>
       <c r="B58">
-        <v>1.162108316436391</v>
+        <v>1.162107247006948</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45940</v>
       </c>
       <c r="B59">
-        <v>1.159735793017401</v>
+        <v>1.159735268080099</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45947</v>
       </c>
       <c r="B60">
-        <v>1.15541665386992</v>
+        <v>1.155416694991266</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45954</v>
       </c>
       <c r="B61">
-        <v>1.148474382192126</v>
+        <v>1.148474742787048</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45961</v>
       </c>
       <c r="B62">
-        <v>1.14314044117129</v>
+        <v>1.143140405323872</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45968</v>
       </c>
       <c r="B63">
-        <v>1.137867573888667</v>
+        <v>1.137866775228273</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>45975</v>
       </c>
       <c r="B64">
-        <v>1.130108566523507</v>
+        <v>1.130106357382811</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>45982</v>
       </c>
       <c r="B65">
-        <v>1.124944364278611</v>
+        <v>1.124941561833626</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45989</v>
       </c>
       <c r="B66">
-        <v>1.129708359054241</v>
+        <v>1.129702169052753</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>45996</v>
       </c>
       <c r="B67">
-        <v>1.136715838876715</v>
+        <v>1.136707029574038</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46003</v>
       </c>
       <c r="B68">
-        <v>1.142562405682758</v>
+        <v>1.142547620306341</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46010</v>
       </c>
       <c r="B69">
-        <v>1.145853981578876</v>
+        <v>1.145836699733562</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46017</v>
       </c>
       <c r="B70">
-        <v>1.145649402218214</v>
+        <v>1.145628701091671</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46024</v>
       </c>
       <c r="B71">
-        <v>1.139879399866936</v>
+        <v>1.139857694792465</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46031</v>
       </c>
       <c r="B72">
-        <v>1.138265335382742</v>
+        <v>1.138242478916047</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46038</v>
       </c>
       <c r="B73">
-        <v>1.138107079267037</v>
+        <v>1.138082854002637</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46045</v>
       </c>
       <c r="B74">
-        <v>1.149898319758895</v>
+        <v>1.149882351027623</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46052</v>
       </c>
       <c r="B75">
-        <v>1.165514856939492</v>
+        <v>1.165504207891909</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46059</v>
       </c>
       <c r="B76">
-        <v>1.165982386762319</v>
+        <v>1.165972383895598</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46066</v>
       </c>
       <c r="B77">
-        <v>1.180569007145244</v>
+        <v>1.180567331461709</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46073</v>
       </c>
       <c r="B78">
-        <v>1.191704103896605</v>
+        <v>1.191712205084553</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46080</v>
       </c>
       <c r="B79">
-        <v>1.199945896387072</v>
+        <v>1.199955660214754</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46087</v>
       </c>
       <c r="B80">
-        <v>1.211771549511749</v>
+        <v>1.211785756015403</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46094</v>
       </c>
       <c r="B81">
-        <v>1.205783443934319</v>
+        <v>1.20578802788464</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46101</v>
       </c>
       <c r="B82">
-        <v>1.206641075999651</v>
+        <v>1.206648802675452</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46108</v>
       </c>
       <c r="B83">
-        <v>1.210505161732895</v>
+        <v>1.210522572286609</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46115</v>
       </c>
       <c r="B84">
-        <v>1.216396339312654</v>
+        <v>1.216421864879601</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46122</v>
       </c>
       <c r="B85">
-        <v>1.222657887461944</v>
+        <v>1.222687359573379</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46129</v>
       </c>
       <c r="B86">
-        <v>1.221190671202506</v>
+        <v>1.221213342085941</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46136</v>
       </c>
       <c r="B87">
-        <v>1.208685200569686</v>
+        <v>1.20870560546458</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46143</v>
       </c>
       <c r="B88">
-        <v>1.200370607726499</v>
+        <v>1.200389919203833</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46150</v>
       </c>
       <c r="B89">
-        <v>1.189652747628241</v>
+        <v>1.189667398397284</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46157</v>
       </c>
       <c r="B90">
-        <v>1.181264662261313</v>
+        <v>1.181277001617744</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46164</v>
       </c>
       <c r="B91">
-        <v>1.175986542057045</v>
+        <v>1.175995818146778</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46171</v>
       </c>
       <c r="B92">
-        <v>1.172456557607374</v>
+        <v>1.172462778959286</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46178</v>
       </c>
       <c r="B93">
-        <v>1.173825102382142</v>
+        <v>1.173835545921631</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46185</v>
       </c>
       <c r="B94">
-        <v>1.169799660456743</v>
+        <v>1.16980628936731</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46192</v>
       </c>
       <c r="B95">
-        <v>1.168594305389605</v>
+        <v>1.168602042356905</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46199</v>
       </c>
       <c r="B96">
-        <v>1.168758576100567</v>
+        <v>1.168771055133871</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46206</v>
       </c>
       <c r="B97">
-        <v>1.166615272896566</v>
+        <v>1.166626021969348</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46213</v>
       </c>
       <c r="B98">
-        <v>1.158335680871494</v>
+        <v>1.158343807962819</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46220</v>
       </c>
       <c r="B99">
-        <v>1.151992010341455</v>
+        <v>1.15200372382346</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46227</v>
       </c>
       <c r="B100">
-        <v>1.147230815735125</v>
+        <v>1.147242366569989</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46234</v>
       </c>
       <c r="B101">
-        <v>1.144437173539274</v>
+        <v>1.144443451339975</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46241</v>
       </c>
       <c r="B102">
-        <v>1.144491297746339</v>
+        <v>1.144489930161446</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46248</v>
       </c>
       <c r="B103">
-        <v>1.145704220554451</v>
+        <v>1.145696369169063</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46255</v>
       </c>
       <c r="B104">
-        <v>1.148186484137866</v>
+        <v>1.148168629257444</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46262</v>
       </c>
       <c r="B105">
-        <v>1.149110915504545</v>
+        <v>1.149085574664139</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46269</v>
       </c>
       <c r="B106">
-        <v>1.147975790339576</v>
+        <v>1.147943629694761</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46276</v>
       </c>
       <c r="B107">
-        <v>1.147052076167456</v>
+        <v>1.147012785045772</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46283</v>
       </c>
       <c r="B108">
-        <v>1.146086949505148</v>
+        <v>1.146045047658611</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46290</v>
       </c>
       <c r="B109">
-        <v>1.144192131232954</v>
+        <v>1.144157642064068</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46297</v>
       </c>
       <c r="B110">
-        <v>1.14208962163806</v>
+        <v>1.142067099592214</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46304</v>
       </c>
       <c r="B111">
-        <v>1.139051802135432</v>
+        <v>1.139047422161958</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46311</v>
       </c>
       <c r="B112">
-        <v>1.136728109692018</v>
+        <v>1.136471291155214</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46318</v>
       </c>
       <c r="B113">
-        <v>1.136700848831051</v>
+        <v>1.136388797627166</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46325</v>
       </c>
       <c r="B114">
-        <v>1.135357424619963</v>
+        <v>1.135106515704038</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46332</v>
       </c>
       <c r="B115">
-        <v>1.134686888347948</v>
+        <v>1.134390735493457</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46339</v>
       </c>
       <c r="B116">
-        <v>1.134324572530685</v>
+        <v>1.133979026925539</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46346</v>
       </c>
       <c r="B117">
-        <v>1.133394978255714</v>
+        <v>1.133030078137428</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46353</v>
       </c>
       <c r="B118">
-        <v>1.126365733788096</v>
+        <v>1.1261449355757</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46360</v>
       </c>
       <c r="B119">
-        <v>1.118654826940057</v>
+        <v>1.118627871350629</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46367</v>
       </c>
       <c r="B120">
-        <v>1.109277478516669</v>
+        <v>1.109557122062947</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46374</v>
       </c>
       <c r="B121">
-        <v>1.089668151155079</v>
+        <v>1.090799569856051</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1362,7 +1362,7 @@
         <v>46381</v>
       </c>
       <c r="B122">
-        <v>1.071149329840895</v>
+        <v>1.073319598691524</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1370,7 +1370,7 @@
         <v>46388</v>
       </c>
       <c r="B123">
-        <v>1.05719201733495</v>
+        <v>1.060641223127828</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1378,7 +1378,7 @@
         <v>46395</v>
       </c>
       <c r="B124">
-        <v>1.060314932764205</v>
+        <v>1.064349089973935</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -1386,7 +1386,7 @@
         <v>46402</v>
       </c>
       <c r="B125">
-        <v>1.075449103162515</v>
+        <v>1.079014734576851</v>
       </c>
     </row>
   </sheetData>
